--- a/Data/Hires/Workday_NewHire_Italy_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_Italy_Regression_PK17.xlsx
@@ -1,20 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{6DFCB5B9-9D75-488A-A68A-5719165F2A4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
+    <workbookView xWindow="1900" yWindow="1900" windowWidth="14400" windowHeight="7360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="128">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -218,12 +233,6 @@
   </si>
   <si>
     <t>Test_1</t>
-  </si>
-  <si>
-    <t>10698912</t>
-  </si>
-  <si>
-    <t>Passed</t>
   </si>
   <si>
     <t>275 Recruitment (Zojez Vizyzi (10279378))</t>
@@ -357,9 +366,6 @@
   </si>
   <si>
     <t>Test_2</t>
-  </si>
-  <si>
-    <t>10698913</t>
   </si>
   <si>
     <t>275 Store Management (Gyzag Hopope (10144587))</t>
@@ -413,59 +419,59 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="9" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="14"/>
       <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="14"/>
-      <name val="Arial"/>
     </font>
     <font>
       <u/>
+      <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF4A4A4A"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <color rgb="FF4A4A4A"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <family val="2"/>
-      <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="7">
@@ -477,13 +483,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.5999938962981048"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.1499984740745262"/>
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -500,7 +506,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.7999816888943144"/>
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -520,22 +526,40 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -928,9 +952,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BR23"/>
-  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="10.81640625" customWidth="1"/>
@@ -989,7 +1013,7 @@
     <col min="58" max="58" width="10.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" spans="1:70" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:70" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1201,99 +1225,95 @@
         <v>66</v>
       </c>
     </row>
-    <row r="2" ht="14.5" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>67</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="8"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="E2" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="F2" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="G2" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="H2" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="I2" t="s">
         <v>73</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="J2" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="J2" s="15" t="s">
+      <c r="L2" s="16">
+        <f t="shared" ref="L2:L3" ca="1" si="0">TODAY()-31</f>
+        <v>45761</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="N2" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="K2" s="15" t="s">
+      <c r="O2" s="17" t="s">
         <v>77</v>
-      </c>
-      <c r="L2" s="16">
-        <f t="shared" ref="L2:L3" si="0">TODAY()-31</f>
-        <v>45752</v>
-      </c>
-      <c r="M2" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="N2" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="O2" s="17" t="s">
-        <v>79</v>
       </c>
       <c r="P2" s="17">
         <v>1</v>
       </c>
       <c r="Q2" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="R2" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="S2" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="T2" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="R2" s="15" t="s">
+      <c r="U2" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="S2" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="T2" s="18" t="s">
+      <c r="V2" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="W2" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="U2" s="19" t="s">
+      <c r="X2" s="20">
+        <f t="shared" ref="X2:X3" ca="1" si="1">L2</f>
+        <v>45761</v>
+      </c>
+      <c r="Y2" s="16">
+        <f t="shared" ref="Y2:Y3" ca="1" si="2">TODAY()+20</f>
+        <v>45812</v>
+      </c>
+      <c r="Z2" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="V2" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="W2" s="15" t="s">
+      <c r="AA2" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="X2" s="20">
-        <f t="shared" ref="X2:X3" si="1">L2</f>
-        <v>45752</v>
-      </c>
-      <c r="Y2" s="16">
-        <f t="shared" ref="Y2:Y3" si="2">TODAY()+20</f>
-        <v>45803</v>
-      </c>
-      <c r="Z2" s="15" t="s">
+      <c r="AB2" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="AA2" s="21" t="s">
+      <c r="AC2" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="AB2" s="22" t="s">
+      <c r="AD2" s="22" t="s">
         <v>87</v>
-      </c>
-      <c r="AC2" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="AD2" s="22" t="s">
-        <v>89</v>
       </c>
       <c r="AE2" s="11">
         <v>275</v>
@@ -1305,215 +1325,211 @@
         <v>40</v>
       </c>
       <c r="AH2" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AJ2" s="26" t="s">
         <v>90</v>
       </c>
-      <c r="AI2" t="s">
+      <c r="AK2" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="AJ2" s="26" t="s">
+      <c r="AL2" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="AK2" s="15" t="s">
+      <c r="AM2" t="s">
         <v>93</v>
       </c>
-      <c r="AL2" s="15" t="s">
+      <c r="AN2" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="AM2" t="s">
+      <c r="AO2" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="AN2" s="15" t="s">
+      <c r="AP2" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="AO2" s="15" t="s">
+      <c r="AQ2" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="AP2" s="15" t="s">
+      <c r="AR2" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="AS2" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="AQ2" s="27" t="s">
+      <c r="AT2" s="18">
+        <f t="shared" ref="AT2:AT3" ca="1" si="3">X2-1</f>
+        <v>45760</v>
+      </c>
+      <c r="AU2" s="18">
+        <f t="shared" ref="AU2:AU3" ca="1" si="4">X2-1</f>
+        <v>45760</v>
+      </c>
+      <c r="AV2" s="29" t="str">
+        <f t="shared" ref="AV2:AV3" si="5">AJ2</f>
+        <v>N/A</v>
+      </c>
+      <c r="AW2" s="30" t="s">
+        <v>90</v>
+      </c>
+      <c r="AX2" s="30" t="s">
+        <v>90</v>
+      </c>
+      <c r="AY2" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="AZ2" s="31" t="s">
         <v>99</v>
       </c>
-      <c r="AR2" s="22" t="s">
-        <v>92</v>
-      </c>
-      <c r="AS2" s="28" t="s">
+      <c r="BA2" s="31" t="str">
+        <f ca="1">AZ9</f>
+        <v>AB66274JC</v>
+      </c>
+      <c r="BB2" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="BC2" s="31" t="s">
         <v>100</v>
       </c>
-      <c r="AT2" s="18">
-        <f t="shared" ref="AT2:AT3" si="3">X2-1</f>
-        <v>45751</v>
-      </c>
-      <c r="AU2" s="18">
-        <f t="shared" ref="AU2:AU3" si="4">X2-1</f>
-        <v>45751</v>
-      </c>
-      <c r="AV2" s="29">
-        <f t="shared" ref="AV2:AV3" si="5">AJ2</f>
-        <v>NaN</v>
-      </c>
-      <c r="AW2" s="30" t="s">
-        <v>92</v>
-      </c>
-      <c r="AX2" s="30" t="s">
-        <v>92</v>
-      </c>
-      <c r="AY2" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="AZ2" s="31" t="s">
+      <c r="BD2" s="32" t="str">
+        <f ca="1">BH9</f>
+        <v>MTKBNN10D10A466A</v>
+      </c>
+      <c r="BE2" t="s">
         <v>101</v>
-      </c>
-      <c r="BA2" s="31">
-        <f>AZ9</f>
-        <v>NaN</v>
-      </c>
-      <c r="BB2" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="BC2" s="31" t="s">
-        <v>102</v>
-      </c>
-      <c r="BD2" s="32" t="str">
-        <f>BH9</f>
-        <v>MTKBNN10D10A732A</v>
-      </c>
-      <c r="BE2" t="s">
-        <v>103</v>
       </c>
       <c r="BF2" s="33">
         <v>35591</v>
       </c>
       <c r="BG2" s="11" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="BH2" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="BI2" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="BJ2" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="BK2" s="33" t="s">
         <v>104</v>
       </c>
-      <c r="BI2" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="BJ2" s="11" t="s">
+      <c r="BL2" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="BM2" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="BK2" s="33" t="s">
+      <c r="BN2" s="31" t="s">
         <v>106</v>
       </c>
-      <c r="BL2" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="BM2" s="11" t="s">
+      <c r="BO2" s="31" t="s">
         <v>107</v>
       </c>
-      <c r="BN2" s="31" t="s">
+      <c r="BP2" s="31" t="s">
         <v>108</v>
       </c>
-      <c r="BO2" s="31" t="s">
+      <c r="BQ2" s="31" t="s">
         <v>109</v>
       </c>
-      <c r="BP2" s="31" t="s">
+      <c r="BR2" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="BQ2" s="31" t="s">
+    </row>
+    <row r="3" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>111</v>
       </c>
-      <c r="BR2" s="15" t="s">
+      <c r="B3" s="8"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="10" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="3" ht="14.5" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="E3" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="G3" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="H3" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="I3" t="s">
+        <v>73</v>
+      </c>
+      <c r="J3" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="K3" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="L3" s="16">
+        <f t="shared" ca="1" si="0"/>
+        <v>45761</v>
+      </c>
+      <c r="M3" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="D3" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="G3" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="H3" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="I3" t="s">
-        <v>75</v>
-      </c>
-      <c r="J3" s="15" t="s">
+      <c r="N3" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="K3" s="15" t="s">
+      <c r="O3" s="17" t="s">
         <v>77</v>
-      </c>
-      <c r="L3" s="16">
-        <f t="shared" si="0"/>
-        <v>45752</v>
-      </c>
-      <c r="M3" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="N3" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="O3" s="17" t="s">
-        <v>79</v>
       </c>
       <c r="P3" s="17">
         <v>1</v>
       </c>
       <c r="Q3" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="R3" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="S3" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="T3" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="R3" s="15" t="s">
+      <c r="U3" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="S3" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="T3" s="18" t="s">
+      <c r="V3" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="W3" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="U3" s="19" t="s">
+      <c r="X3" s="20">
+        <f t="shared" ca="1" si="1"/>
+        <v>45761</v>
+      </c>
+      <c r="Y3" s="16">
+        <f t="shared" ca="1" si="2"/>
+        <v>45812</v>
+      </c>
+      <c r="Z3" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="V3" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="W3" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="X3" s="20">
-        <f t="shared" si="1"/>
-        <v>45752</v>
-      </c>
-      <c r="Y3" s="16">
-        <f t="shared" si="2"/>
-        <v>45803</v>
-      </c>
-      <c r="Z3" s="15" t="s">
+      <c r="AA3" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="AB3" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="AA3" s="21" t="s">
-        <v>118</v>
-      </c>
-      <c r="AB3" s="22" t="s">
+      <c r="AC3" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="AD3" s="22" t="s">
         <v>87</v>
-      </c>
-      <c r="AC3" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="AD3" s="22" t="s">
-        <v>89</v>
       </c>
       <c r="AE3" s="11">
         <v>275</v>
@@ -1525,600 +1541,613 @@
         <v>40</v>
       </c>
       <c r="AH3" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>89</v>
+      </c>
+      <c r="AJ3" s="26" t="s">
         <v>90</v>
       </c>
-      <c r="AI3" t="s">
+      <c r="AK3" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="AJ3" s="26" t="s">
-        <v>92</v>
-      </c>
-      <c r="AK3" s="15" t="s">
-        <v>93</v>
-      </c>
       <c r="AL3" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AN3" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="AO3" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="AP3" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="AM3" t="s">
-        <v>121</v>
-      </c>
-      <c r="AN3" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="AO3" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="AP3" s="15" t="s">
-        <v>123</v>
-      </c>
       <c r="AQ3" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="AR3" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="AS3" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="AT3" s="18">
+        <f t="shared" ca="1" si="3"/>
+        <v>45760</v>
+      </c>
+      <c r="AU3" s="18">
+        <f t="shared" ca="1" si="4"/>
+        <v>45760</v>
+      </c>
+      <c r="AV3" s="29" t="str">
+        <f t="shared" si="5"/>
+        <v>N/A</v>
+      </c>
+      <c r="AW3" s="30" t="s">
+        <v>90</v>
+      </c>
+      <c r="AX3" s="30" t="s">
+        <v>90</v>
+      </c>
+      <c r="AY3" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="AZ3" s="31" t="s">
         <v>99</v>
       </c>
-      <c r="AR3" s="22" t="s">
-        <v>92</v>
-      </c>
-      <c r="AS3" s="28" t="s">
+      <c r="BA3" s="31" t="str">
+        <f ca="1">AZ10</f>
+        <v>BA42984CJ</v>
+      </c>
+      <c r="BB3" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="BC3" s="31" t="s">
         <v>100</v>
       </c>
-      <c r="AT3" s="18">
-        <f t="shared" si="3"/>
-        <v>45751</v>
-      </c>
-      <c r="AU3" s="18">
-        <f t="shared" si="4"/>
-        <v>45751</v>
-      </c>
-      <c r="AV3" s="29">
-        <f t="shared" si="5"/>
-        <v>NaN</v>
-      </c>
-      <c r="AW3" s="30" t="s">
-        <v>92</v>
-      </c>
-      <c r="AX3" s="30" t="s">
-        <v>92</v>
-      </c>
-      <c r="AY3" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="AZ3" s="31" t="s">
+      <c r="BD3" s="32" t="str">
+        <f ca="1">BH10</f>
+        <v>MTKNBN20D20A859A</v>
+      </c>
+      <c r="BE3" t="s">
         <v>101</v>
-      </c>
-      <c r="BA3" s="31">
-        <f>AZ10</f>
-        <v>NaN</v>
-      </c>
-      <c r="BB3" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="BC3" s="31" t="s">
-        <v>102</v>
-      </c>
-      <c r="BD3" s="32" t="str">
-        <f>BH10</f>
-        <v>MTKNBN20D20A916A</v>
-      </c>
-      <c r="BE3" t="s">
-        <v>103</v>
       </c>
       <c r="BF3" s="33">
         <v>35591</v>
       </c>
       <c r="BG3" s="11" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="BH3" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="BI3" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="BJ3" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="BK3" s="33" t="s">
         <v>104</v>
       </c>
-      <c r="BI3" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="BJ3" s="11" t="s">
+      <c r="BL3" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="BM3" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="BK3" s="33" t="s">
+      <c r="BN3" s="31" t="s">
         <v>106</v>
       </c>
-      <c r="BL3" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="BM3" s="11" t="s">
+      <c r="BO3" s="31" t="s">
         <v>107</v>
       </c>
-      <c r="BN3" s="31" t="s">
+      <c r="BP3" s="31" t="s">
         <v>108</v>
       </c>
-      <c r="BO3" s="31" t="s">
+      <c r="BQ3" s="31" t="s">
         <v>109</v>
       </c>
-      <c r="BP3" s="31" t="s">
+      <c r="BR3" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="BQ3" s="31" t="s">
-        <v>111</v>
-      </c>
-      <c r="BR3" s="15" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="4" spans="3:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:70" x14ac:dyDescent="0.25">
       <c r="C4" s="9"/>
       <c r="AZ4" s="7"/>
       <c r="BA4" s="34"/>
     </row>
-    <row r="5" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:70" x14ac:dyDescent="0.25">
       <c r="C5" s="9"/>
     </row>
-    <row r="6" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:70" x14ac:dyDescent="0.25">
       <c r="C6" s="9"/>
     </row>
-    <row r="7" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:70" x14ac:dyDescent="0.25">
       <c r="C7" s="9"/>
     </row>
-    <row r="8" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:70" x14ac:dyDescent="0.25">
       <c r="C8" s="9"/>
     </row>
-    <row r="9" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C9" s="9"/>
       <c r="AW9" t="s">
+        <v>121</v>
+      </c>
+      <c r="AX9">
+        <f t="array" aca="1" ref="AX9:AX23" ca="1">_xlfn.RANDARRAY(15,1,12345,99999,TRUE)</f>
+        <v>66274</v>
+      </c>
+      <c r="AY9" t="s">
+        <v>122</v>
+      </c>
+      <c r="AZ9" t="str">
+        <f ca="1">AW9&amp;AX9&amp;AY9</f>
+        <v>AB66274JC</v>
+      </c>
+      <c r="BD9" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="BE9">
+        <f t="array" aca="1" ref="BE9:BE23" ca="1">_xlfn.RANDARRAY(15,1,123,999,TRUE)</f>
+        <v>466</v>
+      </c>
+      <c r="BG9" t="s">
         <v>124</v>
       </c>
-      <c r="AX9">
-        <f t="array" ref="AX9:AX23">_xlfn.RANDARRAY(15,1,12345,99999,TRUE)</f>
-        <v>67221</v>
-      </c>
-      <c r="AY9" t="s">
-        <v>125</v>
-      </c>
-      <c r="AZ9" t="str">
-        <f>AW9&amp;AX9&amp;AY9</f>
-        <v>AB67221JC</v>
-      </c>
-      <c r="BD9" s="32" t="s">
-        <v>126</v>
-      </c>
-      <c r="BE9">
-        <f t="array" ref="BE9:BE23">_xlfn.RANDARRAY(15,1,123,999,TRUE)</f>
-        <v>732</v>
-      </c>
-      <c r="BG9" t="s">
-        <v>127</v>
-      </c>
       <c r="BH9" t="str">
-        <f>BD9&amp;BE9&amp;BF9&amp;BG9</f>
-        <v>MTKBNN10D10A732A</v>
-      </c>
-    </row>
-    <row r="10" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
+        <f ca="1">BD9&amp;BE9&amp;BF9&amp;BG9</f>
+        <v>MTKBNN10D10A466A</v>
+      </c>
+    </row>
+    <row r="10" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C10" s="9"/>
       <c r="AW10" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="AX10">
-        <v>31138</v>
+        <f ca="1"/>
+        <v>42984</v>
       </c>
       <c r="AY10" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="AZ10" t="str">
-        <f t="shared" ref="AZ10:AZ23" si="6">AW10&amp;AX10&amp;AY10</f>
-        <v>BA31138CJ</v>
+        <f t="shared" ref="AZ10:AZ23" ca="1" si="6">AW10&amp;AX10&amp;AY10</f>
+        <v>BA42984CJ</v>
       </c>
       <c r="BD10" s="32" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="BE10">
-        <v>916</v>
+        <f ca="1"/>
+        <v>859</v>
       </c>
       <c r="BG10" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="BH10" t="str">
-        <f t="shared" ref="BH10:BH23" si="7">BD10&amp;BE10&amp;BF10&amp;BG10</f>
-        <v>MTKNBN20D20A916A</v>
-      </c>
-    </row>
-    <row r="11" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
+        <f t="shared" ref="BH10:BH23" ca="1" si="7">BD10&amp;BE10&amp;BF10&amp;BG10</f>
+        <v>MTKNBN20D20A859A</v>
+      </c>
+    </row>
+    <row r="11" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C11" s="9"/>
       <c r="AW11" t="s">
+        <v>121</v>
+      </c>
+      <c r="AX11">
+        <f ca="1"/>
+        <v>37581</v>
+      </c>
+      <c r="AY11" t="s">
+        <v>122</v>
+      </c>
+      <c r="AZ11" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v>AB37581JC</v>
+      </c>
+      <c r="BD11" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="BE11">
+        <f ca="1"/>
+        <v>417</v>
+      </c>
+      <c r="BG11" t="s">
         <v>124</v>
       </c>
-      <c r="AX11">
-        <v>35395</v>
-      </c>
-      <c r="AY11" t="s">
-        <v>125</v>
-      </c>
-      <c r="AZ11" t="str">
-        <f t="shared" si="6"/>
-        <v>AB35395JC</v>
-      </c>
-      <c r="BD11" s="32" t="s">
-        <v>126</v>
-      </c>
-      <c r="BE11">
-        <v>154</v>
-      </c>
-      <c r="BG11" t="s">
-        <v>127</v>
-      </c>
       <c r="BH11" t="str">
-        <f t="shared" si="7"/>
-        <v>MTKBNN10D10A154A</v>
-      </c>
-    </row>
-    <row r="12" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>MTKBNN10D10A417A</v>
+      </c>
+    </row>
+    <row r="12" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C12" s="9"/>
       <c r="AW12" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="AX12">
-        <v>93764</v>
+        <f ca="1"/>
+        <v>51706</v>
       </c>
       <c r="AY12" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="AZ12" t="str">
-        <f t="shared" si="6"/>
-        <v>BA93764CJ</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>BA51706CJ</v>
       </c>
       <c r="BD12" s="32" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="BE12">
-        <v>186</v>
+        <f ca="1"/>
+        <v>683</v>
       </c>
       <c r="BG12" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="BH12" t="str">
-        <f t="shared" si="7"/>
-        <v>MTKNBN20D20A186A</v>
-      </c>
-    </row>
-    <row r="13" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>MTKNBN20D20A683A</v>
+      </c>
+    </row>
+    <row r="13" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C13" s="9"/>
       <c r="AW13" t="s">
+        <v>121</v>
+      </c>
+      <c r="AX13">
+        <f ca="1"/>
+        <v>46816</v>
+      </c>
+      <c r="AY13" t="s">
+        <v>122</v>
+      </c>
+      <c r="AZ13" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v>AB46816JC</v>
+      </c>
+      <c r="BD13" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="BE13">
+        <f ca="1"/>
+        <v>701</v>
+      </c>
+      <c r="BG13" t="s">
         <v>124</v>
       </c>
-      <c r="AX13">
-        <v>46148</v>
-      </c>
-      <c r="AY13" t="s">
-        <v>125</v>
-      </c>
-      <c r="AZ13" t="str">
-        <f t="shared" si="6"/>
-        <v>AB46148JC</v>
-      </c>
-      <c r="BD13" s="32" t="s">
-        <v>126</v>
-      </c>
-      <c r="BE13">
-        <v>513</v>
-      </c>
-      <c r="BG13" t="s">
-        <v>127</v>
-      </c>
       <c r="BH13" t="str">
-        <f t="shared" si="7"/>
-        <v>MTKBNN10D10A513A</v>
-      </c>
-    </row>
-    <row r="14" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>MTKBNN10D10A701A</v>
+      </c>
+    </row>
+    <row r="14" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C14" s="9"/>
       <c r="AW14" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="AX14">
-        <v>12761</v>
+        <f ca="1"/>
+        <v>26906</v>
       </c>
       <c r="AY14" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="AZ14" t="str">
-        <f t="shared" si="6"/>
-        <v>BA12761CJ</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>BA26906CJ</v>
       </c>
       <c r="BD14" s="32" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="BE14">
-        <v>409</v>
+        <f ca="1"/>
+        <v>911</v>
       </c>
       <c r="BG14" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="BH14" t="str">
-        <f t="shared" si="7"/>
-        <v>MTKNBN20D20A409A</v>
-      </c>
-    </row>
-    <row r="15" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>MTKNBN20D20A911A</v>
+      </c>
+    </row>
+    <row r="15" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C15" s="9"/>
       <c r="AW15" t="s">
+        <v>121</v>
+      </c>
+      <c r="AX15">
+        <f ca="1"/>
+        <v>27261</v>
+      </c>
+      <c r="AY15" t="s">
+        <v>122</v>
+      </c>
+      <c r="AZ15" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v>AB27261JC</v>
+      </c>
+      <c r="BD15" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="BE15">
+        <f ca="1"/>
+        <v>867</v>
+      </c>
+      <c r="BG15" t="s">
         <v>124</v>
       </c>
-      <c r="AX15">
-        <v>28757</v>
-      </c>
-      <c r="AY15" t="s">
-        <v>125</v>
-      </c>
-      <c r="AZ15" t="str">
-        <f t="shared" si="6"/>
-        <v>AB28757JC</v>
-      </c>
-      <c r="BD15" s="32" t="s">
-        <v>126</v>
-      </c>
-      <c r="BE15">
-        <v>800</v>
-      </c>
-      <c r="BG15" t="s">
-        <v>127</v>
-      </c>
       <c r="BH15" t="str">
-        <f t="shared" si="7"/>
-        <v>MTKBNN10D10A800A</v>
-      </c>
-    </row>
-    <row r="16" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>MTKBNN10D10A867A</v>
+      </c>
+    </row>
+    <row r="16" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C16" s="9"/>
       <c r="AW16" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="AX16">
-        <v>61490</v>
+        <f ca="1"/>
+        <v>31655</v>
       </c>
       <c r="AY16" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="AZ16" t="str">
-        <f t="shared" si="6"/>
-        <v>BA61490CJ</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>BA31655CJ</v>
       </c>
       <c r="BD16" s="32" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="BE16">
-        <v>787</v>
+        <f ca="1"/>
+        <v>790</v>
       </c>
       <c r="BG16" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="BH16" t="str">
-        <f t="shared" si="7"/>
-        <v>MTKNBN20D20A787A</v>
-      </c>
-    </row>
-    <row r="17" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>MTKNBN20D20A790A</v>
+      </c>
+    </row>
+    <row r="17" spans="3:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C17" s="9"/>
       <c r="AW17" t="s">
+        <v>121</v>
+      </c>
+      <c r="AX17">
+        <f ca="1"/>
+        <v>95736</v>
+      </c>
+      <c r="AY17" t="s">
+        <v>122</v>
+      </c>
+      <c r="AZ17" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v>AB95736JC</v>
+      </c>
+      <c r="BD17" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="BE17">
+        <f ca="1"/>
+        <v>900</v>
+      </c>
+      <c r="BG17" t="s">
         <v>124</v>
       </c>
-      <c r="AX17">
-        <v>50407</v>
-      </c>
-      <c r="AY17" t="s">
-        <v>125</v>
-      </c>
-      <c r="AZ17" t="str">
-        <f t="shared" si="6"/>
-        <v>AB50407JC</v>
-      </c>
-      <c r="BD17" s="32" t="s">
-        <v>126</v>
-      </c>
-      <c r="BE17">
-        <v>913</v>
-      </c>
-      <c r="BG17" t="s">
-        <v>127</v>
-      </c>
       <c r="BH17" t="str">
-        <f t="shared" si="7"/>
-        <v>MTKBNN10D10A913A</v>
-      </c>
-    </row>
-    <row r="18" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>MTKBNN10D10A900A</v>
+      </c>
+    </row>
+    <row r="18" spans="3:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C18" s="9"/>
       <c r="AW18" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="AX18">
-        <v>69664</v>
+        <f ca="1"/>
+        <v>24109</v>
       </c>
       <c r="AY18" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="AZ18" t="str">
-        <f t="shared" si="6"/>
-        <v>BA69664CJ</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>BA24109CJ</v>
       </c>
       <c r="BD18" s="32" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="BE18">
-        <v>233</v>
+        <f ca="1"/>
+        <v>801</v>
       </c>
       <c r="BG18" t="s">
+        <v>124</v>
+      </c>
+      <c r="BH18" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v>MTKNBN20D20A801A</v>
+      </c>
+    </row>
+    <row r="19" spans="3:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AW19" t="s">
+        <v>121</v>
+      </c>
+      <c r="AX19">
+        <f ca="1"/>
+        <v>36437</v>
+      </c>
+      <c r="AY19" t="s">
+        <v>122</v>
+      </c>
+      <c r="AZ19" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v>AB36437JC</v>
+      </c>
+      <c r="BD19" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="BE19">
+        <f ca="1"/>
+        <v>385</v>
+      </c>
+      <c r="BG19" t="s">
+        <v>124</v>
+      </c>
+      <c r="BH19" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v>MTKBNN10D10A385A</v>
+      </c>
+    </row>
+    <row r="20" spans="3:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AW20" t="s">
+        <v>125</v>
+      </c>
+      <c r="AX20">
+        <f ca="1"/>
+        <v>22254</v>
+      </c>
+      <c r="AY20" t="s">
+        <v>126</v>
+      </c>
+      <c r="AZ20" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v>BA22254CJ</v>
+      </c>
+      <c r="BD20" s="32" t="s">
         <v>127</v>
       </c>
-      <c r="BH18" t="str">
-        <f t="shared" si="7"/>
-        <v>MTKNBN20D20A233A</v>
-      </c>
-    </row>
-    <row r="19" ht="14.5" customHeight="1" spans="49:60" x14ac:dyDescent="0.25">
-      <c r="AW19" t="s">
+      <c r="BE20">
+        <f ca="1"/>
+        <v>412</v>
+      </c>
+      <c r="BG20" t="s">
         <v>124</v>
       </c>
-      <c r="AX19">
-        <v>74205</v>
-      </c>
-      <c r="AY19" t="s">
+      <c r="BH20" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v>MTKNBN20D20A412A</v>
+      </c>
+    </row>
+    <row r="21" spans="3:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AW21" t="s">
+        <v>121</v>
+      </c>
+      <c r="AX21">
+        <f ca="1"/>
+        <v>70907</v>
+      </c>
+      <c r="AY21" t="s">
+        <v>122</v>
+      </c>
+      <c r="AZ21" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v>AB70907JC</v>
+      </c>
+      <c r="BD21" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="BE21">
+        <f ca="1"/>
+        <v>930</v>
+      </c>
+      <c r="BG21" t="s">
+        <v>124</v>
+      </c>
+      <c r="BH21" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v>MTKBNN10D10A930A</v>
+      </c>
+    </row>
+    <row r="22" spans="3:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AW22" t="s">
         <v>125</v>
       </c>
-      <c r="AZ19" t="str">
-        <f t="shared" si="6"/>
-        <v>AB74205JC</v>
-      </c>
-      <c r="BD19" s="32" t="s">
+      <c r="AX22">
+        <f ca="1"/>
+        <v>70838</v>
+      </c>
+      <c r="AY22" t="s">
         <v>126</v>
       </c>
-      <c r="BE19">
-        <v>547</v>
-      </c>
-      <c r="BG19" t="s">
+      <c r="AZ22" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v>BA70838CJ</v>
+      </c>
+      <c r="BD22" s="32" t="s">
         <v>127</v>
       </c>
-      <c r="BH19" t="str">
-        <f t="shared" si="7"/>
-        <v>MTKBNN10D10A547A</v>
-      </c>
-    </row>
-    <row r="20" ht="14.5" customHeight="1" spans="49:60" x14ac:dyDescent="0.25">
-      <c r="AW20" t="s">
-        <v>128</v>
-      </c>
-      <c r="AX20">
-        <v>19370</v>
-      </c>
-      <c r="AY20" t="s">
-        <v>129</v>
-      </c>
-      <c r="AZ20" t="str">
-        <f t="shared" si="6"/>
-        <v>BA19370CJ</v>
-      </c>
-      <c r="BD20" s="32" t="s">
-        <v>130</v>
-      </c>
-      <c r="BE20">
-        <v>208</v>
-      </c>
-      <c r="BG20" t="s">
-        <v>127</v>
-      </c>
-      <c r="BH20" t="str">
-        <f t="shared" si="7"/>
-        <v>MTKNBN20D20A208A</v>
-      </c>
-    </row>
-    <row r="21" ht="14.5" customHeight="1" spans="49:60" x14ac:dyDescent="0.25">
-      <c r="AW21" t="s">
+      <c r="BE22">
+        <f ca="1"/>
+        <v>879</v>
+      </c>
+      <c r="BG22" t="s">
         <v>124</v>
       </c>
-      <c r="AX21">
-        <v>64579</v>
-      </c>
-      <c r="AY21" t="s">
-        <v>125</v>
-      </c>
-      <c r="AZ21" t="str">
-        <f t="shared" si="6"/>
-        <v>AB64579JC</v>
-      </c>
-      <c r="BD21" s="32" t="s">
-        <v>126</v>
-      </c>
-      <c r="BE21">
-        <v>559</v>
-      </c>
-      <c r="BG21" t="s">
-        <v>127</v>
-      </c>
-      <c r="BH21" t="str">
-        <f t="shared" si="7"/>
-        <v>MTKBNN10D10A559A</v>
-      </c>
-    </row>
-    <row r="22" ht="14.5" customHeight="1" spans="49:60" x14ac:dyDescent="0.25">
-      <c r="AW22" t="s">
-        <v>128</v>
-      </c>
-      <c r="AX22">
-        <v>51258</v>
-      </c>
-      <c r="AY22" t="s">
-        <v>129</v>
-      </c>
-      <c r="AZ22" t="str">
-        <f t="shared" si="6"/>
-        <v>BA51258CJ</v>
-      </c>
-      <c r="BD22" s="32" t="s">
-        <v>130</v>
-      </c>
-      <c r="BE22">
-        <v>795</v>
-      </c>
-      <c r="BG22" t="s">
-        <v>127</v>
-      </c>
       <c r="BH22" t="str">
-        <f t="shared" si="7"/>
-        <v>MTKNBN20D20A795A</v>
-      </c>
-    </row>
-    <row r="23" ht="14.5" customHeight="1" spans="49:60" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>MTKNBN20D20A879A</v>
+      </c>
+    </row>
+    <row r="23" spans="3:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="AW23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AX23">
+        <f ca="1"/>
+        <v>60727</v>
+      </c>
+      <c r="AY23" t="s">
+        <v>122</v>
+      </c>
+      <c r="AZ23" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v>AB60727JC</v>
+      </c>
+      <c r="BD23" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="BE23">
+        <f ca="1"/>
+        <v>773</v>
+      </c>
+      <c r="BG23" t="s">
         <v>124</v>
       </c>
-      <c r="AX23">
-        <v>59352</v>
-      </c>
-      <c r="AY23" t="s">
-        <v>125</v>
-      </c>
-      <c r="AZ23" t="str">
-        <f t="shared" si="6"/>
-        <v>AB59352JC</v>
-      </c>
-      <c r="BD23" s="32" t="s">
-        <v>126</v>
-      </c>
-      <c r="BE23">
-        <v>163</v>
-      </c>
-      <c r="BG23" t="s">
-        <v>127</v>
-      </c>
       <c r="BH23" t="str">
-        <f t="shared" si="7"/>
-        <v>MTKBNN10D10A163A</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>MTKBNN10D10A773A</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AS2:AS3">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BQ2:BQ3">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K3">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S3">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V3">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2:Z3">
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AS2:AS3 Z2:Z3 V2:V3 S2:S3 K2:K3 BQ2:BQ3" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="I2" r:id="rId1"/>
-    <hyperlink ref="U2" r:id="rId2"/>
-    <hyperlink ref="AH2" r:id="rId3"/>
-    <hyperlink ref="I3" r:id="rId4"/>
-    <hyperlink ref="U3" r:id="rId5"/>
+    <hyperlink ref="I2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="U2" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="AH2" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="I3" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="U3" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
--- a/Data/Hires/Workday_NewHire_Italy_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_Italy_Regression_PK17.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{6DFCB5B9-9D75-488A-A68A-5719165F2A4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{A1F4E331-DDCB-4EBB-91C0-95D33468FF79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="1900" windowWidth="14400" windowHeight="7360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="131">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -235,6 +235,12 @@
     <t>Test_1</t>
   </si>
   <si>
+    <t>10699100</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
     <t>275 Recruitment (Zojez Vizyzi (10279378))</t>
   </si>
   <si>
@@ -244,10 +250,10 @@
     <t>Mr</t>
   </si>
   <si>
-    <t>Alexander</t>
-  </si>
-  <si>
-    <t>Harvey</t>
+    <t>Jessika</t>
+  </si>
+  <si>
+    <t>Stoltenberg</t>
   </si>
   <si>
     <t>067898707</t>
@@ -368,16 +374,19 @@
     <t>Test_2</t>
   </si>
   <si>
+    <t>10699101</t>
+  </si>
+  <si>
     <t>275 Store Management (Gyzag Hopope (10144587))</t>
   </si>
   <si>
-    <t>Tre</t>
-  </si>
-  <si>
-    <t>Yundt</t>
-  </si>
-  <si>
-    <t>Auto 82277498</t>
+    <t>Madelyn</t>
+  </si>
+  <si>
+    <t>Wiza</t>
+  </si>
+  <si>
+    <t>Auto 81372428</t>
   </si>
   <si>
     <t>Assistant Manager</t>
@@ -1229,91 +1238,95 @@
       <c r="A2" t="s">
         <v>67</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="9"/>
+      <c r="B2" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>69</v>
+      </c>
       <c r="D2" s="10" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H2" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J2" s="15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K2" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="L2" s="16">
         <f t="shared" ref="L2:L3" ca="1" si="0">TODAY()-31</f>
-        <v>45761</v>
+        <v>45762</v>
       </c>
       <c r="M2" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N2" s="17" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="O2" s="17" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="P2" s="17">
         <v>1</v>
       </c>
       <c r="Q2" s="15" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="R2" s="15" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="S2" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="T2" s="18" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="U2" s="19" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="V2" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="W2" s="15" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="X2" s="20">
         <f t="shared" ref="X2:X3" ca="1" si="1">L2</f>
-        <v>45761</v>
+        <v>45762</v>
       </c>
       <c r="Y2" s="16">
         <f t="shared" ref="Y2:Y3" ca="1" si="2">TODAY()+20</f>
-        <v>45812</v>
+        <v>45813</v>
       </c>
       <c r="Z2" s="15" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AA2" s="21" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AB2" s="22" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AC2" s="23" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AD2" s="22" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AE2" s="11">
         <v>275</v>
@@ -1325,211 +1338,215 @@
         <v>40</v>
       </c>
       <c r="AH2" s="25" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AI2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AJ2" s="26" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AK2" s="15" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AL2" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AN2" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="AO2" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="AP2" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="AQ2" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="AR2" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="AM2" t="s">
-        <v>93</v>
-      </c>
-      <c r="AN2" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="AO2" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="AP2" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="AQ2" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="AR2" s="22" t="s">
-        <v>90</v>
-      </c>
       <c r="AS2" s="28" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AT2" s="18">
         <f t="shared" ref="AT2:AT3" ca="1" si="3">X2-1</f>
-        <v>45760</v>
+        <v>45761</v>
       </c>
       <c r="AU2" s="18">
         <f t="shared" ref="AU2:AU3" ca="1" si="4">X2-1</f>
-        <v>45760</v>
+        <v>45761</v>
       </c>
       <c r="AV2" s="29" t="str">
         <f t="shared" ref="AV2:AV3" si="5">AJ2</f>
         <v>N/A</v>
       </c>
       <c r="AW2" s="30" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AX2" s="30" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AY2" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AZ2" s="31" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="BA2" s="31" t="str">
         <f ca="1">AZ9</f>
-        <v>AB66274JC</v>
+        <v>AB72120JC</v>
       </c>
       <c r="BB2" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="BC2" s="31" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="BD2" s="32" t="str">
         <f ca="1">BH9</f>
-        <v>MTKBNN10D10A466A</v>
+        <v>MTKBNN10D10A140A</v>
       </c>
       <c r="BE2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="BF2" s="33">
         <v>35591</v>
       </c>
       <c r="BG2" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="BH2" s="11" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="BI2" s="11" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="BJ2" s="11" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="BK2" s="33" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="BL2" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="BM2" s="11" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="BN2" s="31" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="BO2" s="31" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="BP2" s="31" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="BQ2" s="31" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="BR2" s="15" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>111</v>
-      </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="9"/>
+        <v>113</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>69</v>
+      </c>
       <c r="D3" s="10" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="H3" s="14" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="I3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="L3" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>45761</v>
+        <v>45762</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N3" s="17" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="O3" s="17" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="P3" s="17">
         <v>1</v>
       </c>
       <c r="Q3" s="15" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="R3" s="15" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="S3" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="T3" s="18" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="U3" s="19" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="V3" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="W3" s="15" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="X3" s="20">
         <f t="shared" ca="1" si="1"/>
-        <v>45761</v>
+        <v>45762</v>
       </c>
       <c r="Y3" s="16">
         <f t="shared" ca="1" si="2"/>
-        <v>45812</v>
+        <v>45813</v>
       </c>
       <c r="Z3" s="15" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AA3" s="21" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="AB3" s="22" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AC3" s="23" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="AD3" s="22" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AE3" s="11">
         <v>275</v>
@@ -1541,120 +1558,120 @@
         <v>40</v>
       </c>
       <c r="AH3" s="25" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AI3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AJ3" s="26" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AK3" s="15" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AL3" s="15" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="AM3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AN3" s="15" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AO3" s="15" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="AP3" s="15" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="AQ3" s="27" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AR3" s="22" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AS3" s="28" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AT3" s="18">
         <f t="shared" ca="1" si="3"/>
-        <v>45760</v>
+        <v>45761</v>
       </c>
       <c r="AU3" s="18">
         <f t="shared" ca="1" si="4"/>
-        <v>45760</v>
+        <v>45761</v>
       </c>
       <c r="AV3" s="29" t="str">
         <f t="shared" si="5"/>
         <v>N/A</v>
       </c>
       <c r="AW3" s="30" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AX3" s="30" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AY3" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AZ3" s="31" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="BA3" s="31" t="str">
         <f ca="1">AZ10</f>
-        <v>BA42984CJ</v>
+        <v>BA41264CJ</v>
       </c>
       <c r="BB3" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="BC3" s="31" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="BD3" s="32" t="str">
         <f ca="1">BH10</f>
-        <v>MTKNBN20D20A859A</v>
+        <v>MTKNBN20D20A704A</v>
       </c>
       <c r="BE3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="BF3" s="33">
         <v>35591</v>
       </c>
       <c r="BG3" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="BH3" s="11" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="BI3" s="11" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="BJ3" s="11" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="BK3" s="33" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="BL3" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="BM3" s="11" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="BN3" s="31" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="BO3" s="31" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="BP3" s="31" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="BQ3" s="31" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="BR3" s="15" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:70" x14ac:dyDescent="0.25">
@@ -1677,461 +1694,461 @@
     <row r="9" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C9" s="9"/>
       <c r="AW9" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="AX9">
         <f t="array" aca="1" ref="AX9:AX23" ca="1">_xlfn.RANDARRAY(15,1,12345,99999,TRUE)</f>
-        <v>66274</v>
+        <v>72120</v>
       </c>
       <c r="AY9" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="AZ9" t="str">
         <f ca="1">AW9&amp;AX9&amp;AY9</f>
-        <v>AB66274JC</v>
+        <v>AB72120JC</v>
       </c>
       <c r="BD9" s="32" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="BE9">
         <f t="array" aca="1" ref="BE9:BE23" ca="1">_xlfn.RANDARRAY(15,1,123,999,TRUE)</f>
-        <v>466</v>
+        <v>140</v>
       </c>
       <c r="BG9" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="BH9" t="str">
         <f ca="1">BD9&amp;BE9&amp;BF9&amp;BG9</f>
-        <v>MTKBNN10D10A466A</v>
+        <v>MTKBNN10D10A140A</v>
       </c>
     </row>
     <row r="10" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C10" s="9"/>
       <c r="AW10" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="AX10">
         <f ca="1"/>
-        <v>42984</v>
+        <v>41264</v>
       </c>
       <c r="AY10" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="AZ10" t="str">
         <f t="shared" ref="AZ10:AZ23" ca="1" si="6">AW10&amp;AX10&amp;AY10</f>
-        <v>BA42984CJ</v>
+        <v>BA41264CJ</v>
       </c>
       <c r="BD10" s="32" t="s">
+        <v>130</v>
+      </c>
+      <c r="BE10">
+        <f ca="1"/>
+        <v>704</v>
+      </c>
+      <c r="BG10" t="s">
         <v>127</v>
-      </c>
-      <c r="BE10">
-        <f ca="1"/>
-        <v>859</v>
-      </c>
-      <c r="BG10" t="s">
-        <v>124</v>
       </c>
       <c r="BH10" t="str">
         <f t="shared" ref="BH10:BH23" ca="1" si="7">BD10&amp;BE10&amp;BF10&amp;BG10</f>
-        <v>MTKNBN20D20A859A</v>
+        <v>MTKNBN20D20A704A</v>
       </c>
     </row>
     <row r="11" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C11" s="9"/>
       <c r="AW11" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="AX11">
         <f ca="1"/>
-        <v>37581</v>
+        <v>43448</v>
       </c>
       <c r="AY11" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="AZ11" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>AB37581JC</v>
+        <v>AB43448JC</v>
       </c>
       <c r="BD11" s="32" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="BE11">
         <f ca="1"/>
-        <v>417</v>
+        <v>988</v>
       </c>
       <c r="BG11" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="BH11" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>MTKBNN10D10A417A</v>
-      </c>
-    </row>
-    <row r="12" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>MTKBNN10D10A988A</v>
+      </c>
+    </row>
+    <row r="12" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C12" s="9"/>
       <c r="AW12" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="AX12">
         <f ca="1"/>
-        <v>51706</v>
+        <v>32808</v>
       </c>
       <c r="AY12" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="AZ12" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>BA51706CJ</v>
+        <v>BA32808CJ</v>
       </c>
       <c r="BD12" s="32" t="s">
+        <v>130</v>
+      </c>
+      <c r="BE12">
+        <f ca="1"/>
+        <v>527</v>
+      </c>
+      <c r="BG12" t="s">
         <v>127</v>
-      </c>
-      <c r="BE12">
-        <f ca="1"/>
-        <v>683</v>
-      </c>
-      <c r="BG12" t="s">
-        <v>124</v>
       </c>
       <c r="BH12" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>MTKNBN20D20A683A</v>
-      </c>
-    </row>
-    <row r="13" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>MTKNBN20D20A527A</v>
+      </c>
+    </row>
+    <row r="13" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C13" s="9"/>
       <c r="AW13" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="AX13">
         <f ca="1"/>
-        <v>46816</v>
+        <v>44353</v>
       </c>
       <c r="AY13" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="AZ13" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>AB46816JC</v>
+        <v>AB44353JC</v>
       </c>
       <c r="BD13" s="32" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="BE13">
         <f ca="1"/>
-        <v>701</v>
+        <v>127</v>
       </c>
       <c r="BG13" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="BH13" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>MTKBNN10D10A701A</v>
-      </c>
-    </row>
-    <row r="14" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>MTKBNN10D10A127A</v>
+      </c>
+    </row>
+    <row r="14" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C14" s="9"/>
       <c r="AW14" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="AX14">
         <f ca="1"/>
-        <v>26906</v>
+        <v>31190</v>
       </c>
       <c r="AY14" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="AZ14" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>BA26906CJ</v>
+        <v>BA31190CJ</v>
       </c>
       <c r="BD14" s="32" t="s">
+        <v>130</v>
+      </c>
+      <c r="BE14">
+        <f ca="1"/>
+        <v>531</v>
+      </c>
+      <c r="BG14" t="s">
         <v>127</v>
-      </c>
-      <c r="BE14">
-        <f ca="1"/>
-        <v>911</v>
-      </c>
-      <c r="BG14" t="s">
-        <v>124</v>
       </c>
       <c r="BH14" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>MTKNBN20D20A911A</v>
-      </c>
-    </row>
-    <row r="15" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>MTKNBN20D20A531A</v>
+      </c>
+    </row>
+    <row r="15" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C15" s="9"/>
       <c r="AW15" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="AX15">
         <f ca="1"/>
-        <v>27261</v>
+        <v>75833</v>
       </c>
       <c r="AY15" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="AZ15" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>AB27261JC</v>
+        <v>AB75833JC</v>
       </c>
       <c r="BD15" s="32" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="BE15">
         <f ca="1"/>
-        <v>867</v>
+        <v>453</v>
       </c>
       <c r="BG15" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="BH15" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>MTKBNN10D10A867A</v>
-      </c>
-    </row>
-    <row r="16" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>MTKBNN10D10A453A</v>
+      </c>
+    </row>
+    <row r="16" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C16" s="9"/>
       <c r="AW16" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="AX16">
         <f ca="1"/>
-        <v>31655</v>
+        <v>33798</v>
       </c>
       <c r="AY16" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="AZ16" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>BA31655CJ</v>
+        <v>BA33798CJ</v>
       </c>
       <c r="BD16" s="32" t="s">
+        <v>130</v>
+      </c>
+      <c r="BE16">
+        <f ca="1"/>
+        <v>500</v>
+      </c>
+      <c r="BG16" t="s">
         <v>127</v>
-      </c>
-      <c r="BE16">
-        <f ca="1"/>
-        <v>790</v>
-      </c>
-      <c r="BG16" t="s">
-        <v>124</v>
       </c>
       <c r="BH16" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>MTKNBN20D20A790A</v>
-      </c>
-    </row>
-    <row r="17" spans="3:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>MTKNBN20D20A500A</v>
+      </c>
+    </row>
+    <row r="17" spans="3:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C17" s="9"/>
       <c r="AW17" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="AX17">
         <f ca="1"/>
-        <v>95736</v>
+        <v>20836</v>
       </c>
       <c r="AY17" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="AZ17" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>AB95736JC</v>
+        <v>AB20836JC</v>
       </c>
       <c r="BD17" s="32" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="BE17">
         <f ca="1"/>
-        <v>900</v>
+        <v>201</v>
       </c>
       <c r="BG17" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="BH17" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>MTKBNN10D10A900A</v>
-      </c>
-    </row>
-    <row r="18" spans="3:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>MTKBNN10D10A201A</v>
+      </c>
+    </row>
+    <row r="18" spans="3:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C18" s="9"/>
       <c r="AW18" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="AX18">
         <f ca="1"/>
-        <v>24109</v>
+        <v>13360</v>
       </c>
       <c r="AY18" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="AZ18" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>BA24109CJ</v>
+        <v>BA13360CJ</v>
       </c>
       <c r="BD18" s="32" t="s">
+        <v>130</v>
+      </c>
+      <c r="BE18">
+        <f ca="1"/>
+        <v>740</v>
+      </c>
+      <c r="BG18" t="s">
         <v>127</v>
-      </c>
-      <c r="BE18">
-        <f ca="1"/>
-        <v>801</v>
-      </c>
-      <c r="BG18" t="s">
-        <v>124</v>
       </c>
       <c r="BH18" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>MTKNBN20D20A801A</v>
-      </c>
-    </row>
-    <row r="19" spans="3:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>MTKNBN20D20A740A</v>
+      </c>
+    </row>
+    <row r="19" spans="3:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="AW19" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="AX19">
         <f ca="1"/>
-        <v>36437</v>
+        <v>24118</v>
       </c>
       <c r="AY19" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="AZ19" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>AB36437JC</v>
+        <v>AB24118JC</v>
       </c>
       <c r="BD19" s="32" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="BE19">
         <f ca="1"/>
-        <v>385</v>
+        <v>993</v>
       </c>
       <c r="BG19" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="BH19" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>MTKBNN10D10A385A</v>
-      </c>
-    </row>
-    <row r="20" spans="3:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>MTKBNN10D10A993A</v>
+      </c>
+    </row>
+    <row r="20" spans="3:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="AW20" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="AX20">
         <f ca="1"/>
-        <v>22254</v>
+        <v>91330</v>
       </c>
       <c r="AY20" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="AZ20" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>BA22254CJ</v>
+        <v>BA91330CJ</v>
       </c>
       <c r="BD20" s="32" t="s">
+        <v>130</v>
+      </c>
+      <c r="BE20">
+        <f ca="1"/>
+        <v>456</v>
+      </c>
+      <c r="BG20" t="s">
         <v>127</v>
-      </c>
-      <c r="BE20">
-        <f ca="1"/>
-        <v>412</v>
-      </c>
-      <c r="BG20" t="s">
-        <v>124</v>
       </c>
       <c r="BH20" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>MTKNBN20D20A412A</v>
-      </c>
-    </row>
-    <row r="21" spans="3:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>MTKNBN20D20A456A</v>
+      </c>
+    </row>
+    <row r="21" spans="3:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="AW21" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="AX21">
         <f ca="1"/>
-        <v>70907</v>
+        <v>62502</v>
       </c>
       <c r="AY21" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="AZ21" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>AB70907JC</v>
+        <v>AB62502JC</v>
       </c>
       <c r="BD21" s="32" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="BE21">
         <f ca="1"/>
-        <v>930</v>
+        <v>839</v>
       </c>
       <c r="BG21" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="BH21" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>MTKBNN10D10A930A</v>
+        <v>MTKBNN10D10A839A</v>
       </c>
     </row>
     <row r="22" spans="3:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="AW22" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="AX22">
         <f ca="1"/>
-        <v>70838</v>
+        <v>61265</v>
       </c>
       <c r="AY22" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="AZ22" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>BA70838CJ</v>
+        <v>BA61265CJ</v>
       </c>
       <c r="BD22" s="32" t="s">
+        <v>130</v>
+      </c>
+      <c r="BE22">
+        <f ca="1"/>
+        <v>465</v>
+      </c>
+      <c r="BG22" t="s">
         <v>127</v>
-      </c>
-      <c r="BE22">
-        <f ca="1"/>
-        <v>879</v>
-      </c>
-      <c r="BG22" t="s">
-        <v>124</v>
       </c>
       <c r="BH22" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>MTKNBN20D20A879A</v>
+        <v>MTKNBN20D20A465A</v>
       </c>
     </row>
     <row r="23" spans="3:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="AW23" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="AX23">
         <f ca="1"/>
-        <v>60727</v>
+        <v>38541</v>
       </c>
       <c r="AY23" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="AZ23" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>AB60727JC</v>
+        <v>AB38541JC</v>
       </c>
       <c r="BD23" s="32" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="BE23">
         <f ca="1"/>
-        <v>773</v>
+        <v>996</v>
       </c>
       <c r="BG23" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="BH23" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>MTKBNN10D10A773A</v>
+        <v>MTKBNN10D10A996A</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Hires/Workday_NewHire_Italy_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_Italy_Regression_PK17.xlsx
@@ -1,30 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{A1F4E331-DDCB-4EBB-91C0-95D33468FF79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
@@ -235,7 +220,7 @@
     <t>Test_1</t>
   </si>
   <si>
-    <t>10699100</t>
+    <t>10699522</t>
   </si>
   <si>
     <t>Passed</t>
@@ -250,10 +235,10 @@
     <t>Mr</t>
   </si>
   <si>
-    <t>Jessika</t>
-  </si>
-  <si>
-    <t>Stoltenberg</t>
+    <t>Benjamin</t>
+  </si>
+  <si>
+    <t>Wyman</t>
   </si>
   <si>
     <t>067898707</t>
@@ -374,19 +359,19 @@
     <t>Test_2</t>
   </si>
   <si>
-    <t>10699101</t>
+    <t>10699523</t>
   </si>
   <si>
     <t>275 Store Management (Gyzag Hopope (10144587))</t>
   </si>
   <si>
-    <t>Madelyn</t>
-  </si>
-  <si>
-    <t>Wiza</t>
-  </si>
-  <si>
-    <t>Auto 81372428</t>
+    <t>Jayme</t>
+  </si>
+  <si>
+    <t>Runolfsdottir</t>
+  </si>
+  <si>
+    <t>Auto 9304849</t>
   </si>
   <si>
     <t>Assistant Manager</t>
@@ -428,59 +413,59 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11"/>
       <color theme="9" tint="-0.249977111117893"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <color theme="1"/>
+      <family val="2"/>
       <sz val="14"/>
-      <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11"/>
       <color rgb="FF4A4A4A"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -492,13 +477,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.5999938962981048"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <fgColor theme="0" tint="-0.1499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -515,7 +500,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -535,40 +520,22 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
+      <left style="thin"/>
       <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -961,12 +928,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BR23"/>
-  <sheetFormatPr defaultRowHeight="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="10.81640625" customWidth="1"/>
+    <col min="2" max="2" width="65.90625" customWidth="1"/>
     <col min="3" max="3" width="9.36328125" customWidth="1"/>
     <col min="4" max="4" width="22.6328125" customWidth="1"/>
     <col min="5" max="5" width="7.6328125" customWidth="1"/>
@@ -1020,9 +987,10 @@
     <col min="56" max="56" width="22.7265625" customWidth="1"/>
     <col min="57" max="57" width="8.7265625" customWidth="1"/>
     <col min="58" max="58" width="10.453125" customWidth="1"/>
+    <col min="70" max="70" width="39.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:70" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="18" customHeight="1" spans="1:70" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1234,7 +1202,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="2" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" ht="14.5" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>67</v>
       </c>
@@ -1269,8 +1237,8 @@
         <v>77</v>
       </c>
       <c r="L2" s="16">
-        <f t="shared" ref="L2:L3" ca="1" si="0">TODAY()-31</f>
-        <v>45762</v>
+        <f t="shared" ref="L2:L3" si="0">TODAY()-31</f>
+        <v>45779</v>
       </c>
       <c r="M2" s="11" t="s">
         <v>71</v>
@@ -1306,12 +1274,12 @@
         <v>84</v>
       </c>
       <c r="X2" s="20">
-        <f t="shared" ref="X2:X3" ca="1" si="1">L2</f>
-        <v>45762</v>
+        <f t="shared" ref="X2:X3" si="1">L2</f>
+        <v>45779</v>
       </c>
       <c r="Y2" s="16">
-        <f t="shared" ref="Y2:Y3" ca="1" si="2">TODAY()+20</f>
-        <v>45813</v>
+        <f t="shared" ref="Y2:Y3" si="2">TODAY()+20</f>
+        <v>45830</v>
       </c>
       <c r="Z2" s="15" t="s">
         <v>85</v>
@@ -1374,16 +1342,16 @@
         <v>100</v>
       </c>
       <c r="AT2" s="18">
-        <f t="shared" ref="AT2:AT3" ca="1" si="3">X2-1</f>
-        <v>45761</v>
+        <f t="shared" ref="AT2:AT3" si="3">X2-1</f>
+        <v>45778</v>
       </c>
       <c r="AU2" s="18">
-        <f t="shared" ref="AU2:AU3" ca="1" si="4">X2-1</f>
-        <v>45761</v>
-      </c>
-      <c r="AV2" s="29" t="str">
+        <f t="shared" ref="AU2:AU3" si="4">X2-1</f>
+        <v>45778</v>
+      </c>
+      <c r="AV2" s="29">
         <f t="shared" ref="AV2:AV3" si="5">AJ2</f>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AW2" s="30" t="s">
         <v>92</v>
@@ -1397,9 +1365,9 @@
       <c r="AZ2" s="31" t="s">
         <v>101</v>
       </c>
-      <c r="BA2" s="31" t="str">
-        <f ca="1">AZ9</f>
-        <v>AB72120JC</v>
+      <c r="BA2" s="31">
+        <f>AZ9</f>
+        <v>NaN</v>
       </c>
       <c r="BB2" s="11" t="s">
         <v>71</v>
@@ -1408,8 +1376,8 @@
         <v>102</v>
       </c>
       <c r="BD2" s="32" t="str">
-        <f ca="1">BH9</f>
-        <v>MTKBNN10D10A140A</v>
+        <f>BH9</f>
+        <v>MTKBNN10D10A170A</v>
       </c>
       <c r="BE2" t="s">
         <v>103</v>
@@ -1454,7 +1422,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="3" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" ht="14.5" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>113</v>
       </c>
@@ -1489,8 +1457,8 @@
         <v>77</v>
       </c>
       <c r="L3" s="16">
-        <f t="shared" ca="1" si="0"/>
-        <v>45762</v>
+        <f t="shared" si="0"/>
+        <v>45779</v>
       </c>
       <c r="M3" s="11" t="s">
         <v>71</v>
@@ -1526,12 +1494,12 @@
         <v>84</v>
       </c>
       <c r="X3" s="20">
-        <f t="shared" ca="1" si="1"/>
-        <v>45762</v>
+        <f t="shared" si="1"/>
+        <v>45779</v>
       </c>
       <c r="Y3" s="16">
-        <f t="shared" ca="1" si="2"/>
-        <v>45813</v>
+        <f t="shared" si="2"/>
+        <v>45830</v>
       </c>
       <c r="Z3" s="15" t="s">
         <v>85</v>
@@ -1594,16 +1562,16 @@
         <v>100</v>
       </c>
       <c r="AT3" s="18">
-        <f t="shared" ca="1" si="3"/>
-        <v>45761</v>
+        <f t="shared" si="3"/>
+        <v>45778</v>
       </c>
       <c r="AU3" s="18">
-        <f t="shared" ca="1" si="4"/>
-        <v>45761</v>
-      </c>
-      <c r="AV3" s="29" t="str">
+        <f t="shared" si="4"/>
+        <v>45778</v>
+      </c>
+      <c r="AV3" s="29">
         <f t="shared" si="5"/>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AW3" s="30" t="s">
         <v>92</v>
@@ -1617,9 +1585,9 @@
       <c r="AZ3" s="31" t="s">
         <v>101</v>
       </c>
-      <c r="BA3" s="31" t="str">
-        <f ca="1">AZ10</f>
-        <v>BA41264CJ</v>
+      <c r="BA3" s="31">
+        <f>AZ10</f>
+        <v>NaN</v>
       </c>
       <c r="BB3" s="11" t="s">
         <v>71</v>
@@ -1628,8 +1596,8 @@
         <v>102</v>
       </c>
       <c r="BD3" s="32" t="str">
-        <f ca="1">BH10</f>
-        <v>MTKNBN20D20A704A</v>
+        <f>BH10</f>
+        <v>MTKNBN20D20A891A</v>
       </c>
       <c r="BE3" t="s">
         <v>103</v>
@@ -1674,497 +1642,484 @@
         <v>112</v>
       </c>
     </row>
-    <row r="4" spans="1:70" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:53" x14ac:dyDescent="0.25">
       <c r="C4" s="9"/>
       <c r="AZ4" s="7"/>
       <c r="BA4" s="34"/>
     </row>
-    <row r="5" spans="1:70" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C5" s="9"/>
     </row>
-    <row r="6" spans="1:70" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C6" s="9"/>
     </row>
-    <row r="7" spans="1:70" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C7" s="9"/>
     </row>
-    <row r="8" spans="1:70" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C8" s="9"/>
     </row>
-    <row r="9" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
       <c r="C9" s="9"/>
       <c r="AW9" t="s">
         <v>124</v>
       </c>
       <c r="AX9">
-        <f t="array" aca="1" ref="AX9:AX23" ca="1">_xlfn.RANDARRAY(15,1,12345,99999,TRUE)</f>
-        <v>72120</v>
+        <f t="array" ref="AX9:AX23">_xlfn.RANDARRAY(15,1,12345,99999,TRUE)</f>
+        <v>25785</v>
       </c>
       <c r="AY9" t="s">
         <v>125</v>
       </c>
       <c r="AZ9" t="str">
-        <f ca="1">AW9&amp;AX9&amp;AY9</f>
-        <v>AB72120JC</v>
+        <f>AW9&amp;AX9&amp;AY9</f>
+        <v>AB25785JC</v>
       </c>
       <c r="BD9" s="32" t="s">
         <v>126</v>
       </c>
       <c r="BE9">
-        <f t="array" aca="1" ref="BE9:BE23" ca="1">_xlfn.RANDARRAY(15,1,123,999,TRUE)</f>
-        <v>140</v>
+        <f t="array" ref="BE9:BE23">_xlfn.RANDARRAY(15,1,123,999,TRUE)</f>
+        <v>170</v>
       </c>
       <c r="BG9" t="s">
         <v>127</v>
       </c>
       <c r="BH9" t="str">
-        <f ca="1">BD9&amp;BE9&amp;BF9&amp;BG9</f>
-        <v>MTKBNN10D10A140A</v>
-      </c>
-    </row>
-    <row r="10" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
+        <f>BD9&amp;BE9&amp;BF9&amp;BG9</f>
+        <v>MTKBNN10D10A170A</v>
+      </c>
+    </row>
+    <row r="10" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
       <c r="C10" s="9"/>
       <c r="AW10" t="s">
         <v>128</v>
       </c>
       <c r="AX10">
-        <f ca="1"/>
-        <v>41264</v>
+        <v>24890</v>
       </c>
       <c r="AY10" t="s">
         <v>129</v>
       </c>
       <c r="AZ10" t="str">
-        <f t="shared" ref="AZ10:AZ23" ca="1" si="6">AW10&amp;AX10&amp;AY10</f>
-        <v>BA41264CJ</v>
+        <f t="shared" ref="AZ10:AZ23" si="6">AW10&amp;AX10&amp;AY10</f>
+        <v>BA24890CJ</v>
       </c>
       <c r="BD10" s="32" t="s">
         <v>130</v>
       </c>
       <c r="BE10">
-        <f ca="1"/>
-        <v>704</v>
+        <v>891</v>
       </c>
       <c r="BG10" t="s">
         <v>127</v>
       </c>
       <c r="BH10" t="str">
-        <f t="shared" ref="BH10:BH23" ca="1" si="7">BD10&amp;BE10&amp;BF10&amp;BG10</f>
-        <v>MTKNBN20D20A704A</v>
-      </c>
-    </row>
-    <row r="11" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" ref="BH10:BH23" si="7">BD10&amp;BE10&amp;BF10&amp;BG10</f>
+        <v>MTKNBN20D20A891A</v>
+      </c>
+    </row>
+    <row r="11" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
       <c r="C11" s="9"/>
       <c r="AW11" t="s">
         <v>124</v>
       </c>
       <c r="AX11">
-        <f ca="1"/>
-        <v>43448</v>
+        <v>71290</v>
       </c>
       <c r="AY11" t="s">
         <v>125</v>
       </c>
       <c r="AZ11" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>AB43448JC</v>
+        <f t="shared" si="6"/>
+        <v>AB71290JC</v>
       </c>
       <c r="BD11" s="32" t="s">
         <v>126</v>
       </c>
       <c r="BE11">
-        <f ca="1"/>
-        <v>988</v>
+        <v>531</v>
       </c>
       <c r="BG11" t="s">
         <v>127</v>
       </c>
       <c r="BH11" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>MTKBNN10D10A988A</v>
-      </c>
-    </row>
-    <row r="12" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="7"/>
+        <v>MTKBNN10D10A531A</v>
+      </c>
+    </row>
+    <row r="12" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
       <c r="C12" s="9"/>
       <c r="AW12" t="s">
         <v>128</v>
       </c>
       <c r="AX12">
-        <f ca="1"/>
-        <v>32808</v>
+        <v>42997</v>
       </c>
       <c r="AY12" t="s">
         <v>129</v>
       </c>
       <c r="AZ12" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>BA32808CJ</v>
+        <f t="shared" si="6"/>
+        <v>BA42997CJ</v>
       </c>
       <c r="BD12" s="32" t="s">
         <v>130</v>
       </c>
       <c r="BE12">
-        <f ca="1"/>
-        <v>527</v>
+        <v>256</v>
       </c>
       <c r="BG12" t="s">
         <v>127</v>
       </c>
       <c r="BH12" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>MTKNBN20D20A527A</v>
-      </c>
-    </row>
-    <row r="13" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="7"/>
+        <v>MTKNBN20D20A256A</v>
+      </c>
+    </row>
+    <row r="13" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
       <c r="C13" s="9"/>
       <c r="AW13" t="s">
         <v>124</v>
       </c>
       <c r="AX13">
-        <f ca="1"/>
-        <v>44353</v>
+        <v>40177</v>
       </c>
       <c r="AY13" t="s">
         <v>125</v>
       </c>
       <c r="AZ13" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>AB44353JC</v>
+        <f t="shared" si="6"/>
+        <v>AB40177JC</v>
       </c>
       <c r="BD13" s="32" t="s">
         <v>126</v>
       </c>
       <c r="BE13">
-        <f ca="1"/>
-        <v>127</v>
+        <v>525</v>
       </c>
       <c r="BG13" t="s">
         <v>127</v>
       </c>
       <c r="BH13" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>MTKBNN10D10A127A</v>
-      </c>
-    </row>
-    <row r="14" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="7"/>
+        <v>MTKBNN10D10A525A</v>
+      </c>
+    </row>
+    <row r="14" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
       <c r="C14" s="9"/>
       <c r="AW14" t="s">
         <v>128</v>
       </c>
       <c r="AX14">
-        <f ca="1"/>
-        <v>31190</v>
+        <v>16837</v>
       </c>
       <c r="AY14" t="s">
         <v>129</v>
       </c>
       <c r="AZ14" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>BA31190CJ</v>
+        <f t="shared" si="6"/>
+        <v>BA16837CJ</v>
       </c>
       <c r="BD14" s="32" t="s">
         <v>130</v>
       </c>
       <c r="BE14">
-        <f ca="1"/>
-        <v>531</v>
+        <v>562</v>
       </c>
       <c r="BG14" t="s">
         <v>127</v>
       </c>
       <c r="BH14" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>MTKNBN20D20A531A</v>
-      </c>
-    </row>
-    <row r="15" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="7"/>
+        <v>MTKNBN20D20A562A</v>
+      </c>
+    </row>
+    <row r="15" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
       <c r="C15" s="9"/>
       <c r="AW15" t="s">
         <v>124</v>
       </c>
       <c r="AX15">
-        <f ca="1"/>
-        <v>75833</v>
+        <v>24723</v>
       </c>
       <c r="AY15" t="s">
         <v>125</v>
       </c>
       <c r="AZ15" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>AB75833JC</v>
+        <f t="shared" si="6"/>
+        <v>AB24723JC</v>
       </c>
       <c r="BD15" s="32" t="s">
         <v>126</v>
       </c>
       <c r="BE15">
-        <f ca="1"/>
-        <v>453</v>
+        <v>927</v>
       </c>
       <c r="BG15" t="s">
         <v>127</v>
       </c>
       <c r="BH15" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>MTKBNN10D10A453A</v>
-      </c>
-    </row>
-    <row r="16" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="7"/>
+        <v>MTKBNN10D10A927A</v>
+      </c>
+    </row>
+    <row r="16" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
       <c r="C16" s="9"/>
       <c r="AW16" t="s">
         <v>128</v>
       </c>
       <c r="AX16">
-        <f ca="1"/>
-        <v>33798</v>
+        <v>62926</v>
       </c>
       <c r="AY16" t="s">
         <v>129</v>
       </c>
       <c r="AZ16" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>BA33798CJ</v>
+        <f t="shared" si="6"/>
+        <v>BA62926CJ</v>
       </c>
       <c r="BD16" s="32" t="s">
         <v>130</v>
       </c>
       <c r="BE16">
-        <f ca="1"/>
-        <v>500</v>
+        <v>876</v>
       </c>
       <c r="BG16" t="s">
         <v>127</v>
       </c>
       <c r="BH16" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>MTKNBN20D20A500A</v>
-      </c>
-    </row>
-    <row r="17" spans="3:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="7"/>
+        <v>MTKNBN20D20A876A</v>
+      </c>
+    </row>
+    <row r="17" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
       <c r="C17" s="9"/>
       <c r="AW17" t="s">
         <v>124</v>
       </c>
       <c r="AX17">
-        <f ca="1"/>
-        <v>20836</v>
+        <v>59916</v>
       </c>
       <c r="AY17" t="s">
         <v>125</v>
       </c>
       <c r="AZ17" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>AB20836JC</v>
+        <f t="shared" si="6"/>
+        <v>AB59916JC</v>
       </c>
       <c r="BD17" s="32" t="s">
         <v>126</v>
       </c>
       <c r="BE17">
-        <f ca="1"/>
-        <v>201</v>
+        <v>235</v>
       </c>
       <c r="BG17" t="s">
         <v>127</v>
       </c>
       <c r="BH17" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>MTKBNN10D10A201A</v>
-      </c>
-    </row>
-    <row r="18" spans="3:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="7"/>
+        <v>MTKBNN10D10A235A</v>
+      </c>
+    </row>
+    <row r="18" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
       <c r="C18" s="9"/>
       <c r="AW18" t="s">
         <v>128</v>
       </c>
       <c r="AX18">
-        <f ca="1"/>
-        <v>13360</v>
+        <v>98951</v>
       </c>
       <c r="AY18" t="s">
         <v>129</v>
       </c>
       <c r="AZ18" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>BA13360CJ</v>
+        <f t="shared" si="6"/>
+        <v>BA98951CJ</v>
       </c>
       <c r="BD18" s="32" t="s">
         <v>130</v>
       </c>
       <c r="BE18">
-        <f ca="1"/>
-        <v>740</v>
+        <v>363</v>
       </c>
       <c r="BG18" t="s">
         <v>127</v>
       </c>
       <c r="BH18" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>MTKNBN20D20A740A</v>
-      </c>
-    </row>
-    <row r="19" spans="3:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="7"/>
+        <v>MTKNBN20D20A363A</v>
+      </c>
+    </row>
+    <row r="19" ht="14.5" customHeight="1" spans="49:60" x14ac:dyDescent="0.25">
       <c r="AW19" t="s">
         <v>124</v>
       </c>
       <c r="AX19">
-        <f ca="1"/>
-        <v>24118</v>
+        <v>62936</v>
       </c>
       <c r="AY19" t="s">
         <v>125</v>
       </c>
       <c r="AZ19" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>AB24118JC</v>
+        <f t="shared" si="6"/>
+        <v>AB62936JC</v>
       </c>
       <c r="BD19" s="32" t="s">
         <v>126</v>
       </c>
       <c r="BE19">
-        <f ca="1"/>
-        <v>993</v>
+        <v>274</v>
       </c>
       <c r="BG19" t="s">
         <v>127</v>
       </c>
       <c r="BH19" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>MTKBNN10D10A993A</v>
-      </c>
-    </row>
-    <row r="20" spans="3:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="7"/>
+        <v>MTKBNN10D10A274A</v>
+      </c>
+    </row>
+    <row r="20" ht="14.5" customHeight="1" spans="49:60" x14ac:dyDescent="0.25">
       <c r="AW20" t="s">
         <v>128</v>
       </c>
       <c r="AX20">
-        <f ca="1"/>
-        <v>91330</v>
+        <v>22349</v>
       </c>
       <c r="AY20" t="s">
         <v>129</v>
       </c>
       <c r="AZ20" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>BA91330CJ</v>
+        <f t="shared" si="6"/>
+        <v>BA22349CJ</v>
       </c>
       <c r="BD20" s="32" t="s">
         <v>130</v>
       </c>
       <c r="BE20">
-        <f ca="1"/>
-        <v>456</v>
+        <v>892</v>
       </c>
       <c r="BG20" t="s">
         <v>127</v>
       </c>
       <c r="BH20" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>MTKNBN20D20A456A</v>
-      </c>
-    </row>
-    <row r="21" spans="3:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="7"/>
+        <v>MTKNBN20D20A892A</v>
+      </c>
+    </row>
+    <row r="21" ht="14.5" customHeight="1" spans="49:60" x14ac:dyDescent="0.25">
       <c r="AW21" t="s">
         <v>124</v>
       </c>
       <c r="AX21">
-        <f ca="1"/>
-        <v>62502</v>
+        <v>90020</v>
       </c>
       <c r="AY21" t="s">
         <v>125</v>
       </c>
       <c r="AZ21" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>AB62502JC</v>
+        <f t="shared" si="6"/>
+        <v>AB90020JC</v>
       </c>
       <c r="BD21" s="32" t="s">
         <v>126</v>
       </c>
       <c r="BE21">
-        <f ca="1"/>
-        <v>839</v>
+        <v>251</v>
       </c>
       <c r="BG21" t="s">
         <v>127</v>
       </c>
       <c r="BH21" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>MTKBNN10D10A839A</v>
-      </c>
-    </row>
-    <row r="22" spans="3:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="7"/>
+        <v>MTKBNN10D10A251A</v>
+      </c>
+    </row>
+    <row r="22" ht="14.5" customHeight="1" spans="49:60" x14ac:dyDescent="0.25">
       <c r="AW22" t="s">
         <v>128</v>
       </c>
       <c r="AX22">
-        <f ca="1"/>
-        <v>61265</v>
+        <v>93643</v>
       </c>
       <c r="AY22" t="s">
         <v>129</v>
       </c>
       <c r="AZ22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>BA61265CJ</v>
+        <f t="shared" si="6"/>
+        <v>BA93643CJ</v>
       </c>
       <c r="BD22" s="32" t="s">
         <v>130</v>
       </c>
       <c r="BE22">
-        <f ca="1"/>
-        <v>465</v>
+        <v>992</v>
       </c>
       <c r="BG22" t="s">
         <v>127</v>
       </c>
       <c r="BH22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>MTKNBN20D20A465A</v>
-      </c>
-    </row>
-    <row r="23" spans="3:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="7"/>
+        <v>MTKNBN20D20A992A</v>
+      </c>
+    </row>
+    <row r="23" ht="14.5" customHeight="1" spans="49:60" x14ac:dyDescent="0.25">
       <c r="AW23" t="s">
         <v>124</v>
       </c>
       <c r="AX23">
-        <f ca="1"/>
-        <v>38541</v>
+        <v>79028</v>
       </c>
       <c r="AY23" t="s">
         <v>125</v>
       </c>
       <c r="AZ23" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>AB38541JC</v>
+        <f t="shared" si="6"/>
+        <v>AB79028JC</v>
       </c>
       <c r="BD23" s="32" t="s">
         <v>126</v>
       </c>
       <c r="BE23">
-        <f ca="1"/>
-        <v>996</v>
+        <v>155</v>
       </c>
       <c r="BG23" t="s">
         <v>127</v>
       </c>
       <c r="BH23" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>MTKBNN10D10A996A</v>
+        <f t="shared" si="7"/>
+        <v>MTKBNN10D10A155A</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AS2:AS3 Z2:Z3 V2:V3 S2:S3 K2:K3 BQ2:BQ3" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="6">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AS2:AS3">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BQ2:BQ3">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K3">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S3">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V3">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2:Z3">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="I2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="U2" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="AH2" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="I3" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="U3" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="I2" r:id="rId1"/>
+    <hyperlink ref="U2" r:id="rId2"/>
+    <hyperlink ref="AH2" r:id="rId3"/>
+    <hyperlink ref="I3" r:id="rId4"/>
+    <hyperlink ref="U3" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/Data/Hires/Workday_NewHire_Italy_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_Italy_Regression_PK17.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="131">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -220,10 +220,13 @@
     <t>Test_1</t>
   </si>
   <si>
-    <t>10699522</t>
-  </si>
-  <si>
-    <t>Passed</t>
+    <t xml:space="preserve">Test failed for 'Lia Davis' Employee:{10699680}TimeoutError: locator.click: Timeout 30000ms exceeded.
+Call log:
+  [2m- waiting for locator('text=Assign Paygroup for Payroll: Lia Davis')[22m
+</t>
+  </si>
+  <si>
+    <t>Failed</t>
   </si>
   <si>
     <t>275 Recruitment (Zojez Vizyzi (10279378))</t>
@@ -235,10 +238,10 @@
     <t>Mr</t>
   </si>
   <si>
-    <t>Benjamin</t>
-  </si>
-  <si>
-    <t>Wyman</t>
+    <t>Lia</t>
+  </si>
+  <si>
+    <t>Davis</t>
   </si>
   <si>
     <t>067898707</t>
@@ -359,19 +362,19 @@
     <t>Test_2</t>
   </si>
   <si>
-    <t>10699523</t>
+    <t>Passed</t>
   </si>
   <si>
     <t>275 Store Management (Gyzag Hopope (10144587))</t>
   </si>
   <si>
-    <t>Jayme</t>
-  </si>
-  <si>
-    <t>Runolfsdottir</t>
-  </si>
-  <si>
-    <t>Auto 9304849</t>
+    <t>Mia</t>
+  </si>
+  <si>
+    <t>Doyle</t>
+  </si>
+  <si>
+    <t>Auto 4876895</t>
   </si>
   <si>
     <t>Assistant Manager</t>
@@ -495,7 +498,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00FF00"/>
+        <fgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
     <fill>
@@ -1238,7 +1241,7 @@
       </c>
       <c r="L2" s="16">
         <f t="shared" ref="L2:L3" si="0">TODAY()-31</f>
-        <v>45779</v>
+        <v>45788</v>
       </c>
       <c r="M2" s="11" t="s">
         <v>71</v>
@@ -1275,11 +1278,11 @@
       </c>
       <c r="X2" s="20">
         <f t="shared" ref="X2:X3" si="1">L2</f>
-        <v>45779</v>
+        <v>45788</v>
       </c>
       <c r="Y2" s="16">
         <f t="shared" ref="Y2:Y3" si="2">TODAY()+20</f>
-        <v>45830</v>
+        <v>45839</v>
       </c>
       <c r="Z2" s="15" t="s">
         <v>85</v>
@@ -1343,11 +1346,11 @@
       </c>
       <c r="AT2" s="18">
         <f t="shared" ref="AT2:AT3" si="3">X2-1</f>
-        <v>45778</v>
+        <v>45787</v>
       </c>
       <c r="AU2" s="18">
         <f t="shared" ref="AU2:AU3" si="4">X2-1</f>
-        <v>45778</v>
+        <v>45787</v>
       </c>
       <c r="AV2" s="29">
         <f t="shared" ref="AV2:AV3" si="5">AJ2</f>
@@ -1377,7 +1380,7 @@
       </c>
       <c r="BD2" s="32" t="str">
         <f>BH9</f>
-        <v>MTKBNN10D10A170A</v>
+        <v>MTKBNN10D10A183A</v>
       </c>
       <c r="BE2" t="s">
         <v>103</v>
@@ -1426,11 +1429,11 @@
       <c r="A3" t="s">
         <v>113</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="8">
+        <v>10699677</v>
+      </c>
+      <c r="C3" s="9" t="s">
         <v>114</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>69</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>115</v>
@@ -1458,7 +1461,7 @@
       </c>
       <c r="L3" s="16">
         <f t="shared" si="0"/>
-        <v>45779</v>
+        <v>45788</v>
       </c>
       <c r="M3" s="11" t="s">
         <v>71</v>
@@ -1495,11 +1498,11 @@
       </c>
       <c r="X3" s="20">
         <f t="shared" si="1"/>
-        <v>45779</v>
+        <v>45788</v>
       </c>
       <c r="Y3" s="16">
         <f t="shared" si="2"/>
-        <v>45830</v>
+        <v>45839</v>
       </c>
       <c r="Z3" s="15" t="s">
         <v>85</v>
@@ -1563,11 +1566,11 @@
       </c>
       <c r="AT3" s="18">
         <f t="shared" si="3"/>
-        <v>45778</v>
+        <v>45787</v>
       </c>
       <c r="AU3" s="18">
         <f t="shared" si="4"/>
-        <v>45778</v>
+        <v>45787</v>
       </c>
       <c r="AV3" s="29">
         <f t="shared" si="5"/>
@@ -1597,7 +1600,7 @@
       </c>
       <c r="BD3" s="32" t="str">
         <f>BH10</f>
-        <v>MTKNBN20D20A891A</v>
+        <v>MTKNBN20D20A562A</v>
       </c>
       <c r="BE3" t="s">
         <v>103</v>
@@ -1666,28 +1669,28 @@
       </c>
       <c r="AX9">
         <f t="array" ref="AX9:AX23">_xlfn.RANDARRAY(15,1,12345,99999,TRUE)</f>
-        <v>25785</v>
+        <v>87517</v>
       </c>
       <c r="AY9" t="s">
         <v>125</v>
       </c>
       <c r="AZ9" t="str">
         <f>AW9&amp;AX9&amp;AY9</f>
-        <v>AB25785JC</v>
+        <v>AB87517JC</v>
       </c>
       <c r="BD9" s="32" t="s">
         <v>126</v>
       </c>
       <c r="BE9">
         <f t="array" ref="BE9:BE23">_xlfn.RANDARRAY(15,1,123,999,TRUE)</f>
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="BG9" t="s">
         <v>127</v>
       </c>
       <c r="BH9" t="str">
         <f>BD9&amp;BE9&amp;BF9&amp;BG9</f>
-        <v>MTKBNN10D10A170A</v>
+        <v>MTKBNN10D10A183A</v>
       </c>
     </row>
     <row r="10" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
@@ -1696,27 +1699,27 @@
         <v>128</v>
       </c>
       <c r="AX10">
-        <v>24890</v>
+        <v>18396</v>
       </c>
       <c r="AY10" t="s">
         <v>129</v>
       </c>
       <c r="AZ10" t="str">
         <f t="shared" ref="AZ10:AZ23" si="6">AW10&amp;AX10&amp;AY10</f>
-        <v>BA24890CJ</v>
+        <v>BA18396CJ</v>
       </c>
       <c r="BD10" s="32" t="s">
         <v>130</v>
       </c>
       <c r="BE10">
-        <v>891</v>
+        <v>562</v>
       </c>
       <c r="BG10" t="s">
         <v>127</v>
       </c>
       <c r="BH10" t="str">
         <f t="shared" ref="BH10:BH23" si="7">BD10&amp;BE10&amp;BF10&amp;BG10</f>
-        <v>MTKNBN20D20A891A</v>
+        <v>MTKNBN20D20A562A</v>
       </c>
     </row>
     <row r="11" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
@@ -1725,27 +1728,27 @@
         <v>124</v>
       </c>
       <c r="AX11">
-        <v>71290</v>
+        <v>90133</v>
       </c>
       <c r="AY11" t="s">
         <v>125</v>
       </c>
       <c r="AZ11" t="str">
         <f t="shared" si="6"/>
-        <v>AB71290JC</v>
+        <v>AB90133JC</v>
       </c>
       <c r="BD11" s="32" t="s">
         <v>126</v>
       </c>
       <c r="BE11">
-        <v>531</v>
+        <v>196</v>
       </c>
       <c r="BG11" t="s">
         <v>127</v>
       </c>
       <c r="BH11" t="str">
         <f t="shared" si="7"/>
-        <v>MTKBNN10D10A531A</v>
+        <v>MTKBNN10D10A196A</v>
       </c>
     </row>
     <row r="12" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
@@ -1754,27 +1757,27 @@
         <v>128</v>
       </c>
       <c r="AX12">
-        <v>42997</v>
+        <v>54714</v>
       </c>
       <c r="AY12" t="s">
         <v>129</v>
       </c>
       <c r="AZ12" t="str">
         <f t="shared" si="6"/>
-        <v>BA42997CJ</v>
+        <v>BA54714CJ</v>
       </c>
       <c r="BD12" s="32" t="s">
         <v>130</v>
       </c>
       <c r="BE12">
-        <v>256</v>
+        <v>667</v>
       </c>
       <c r="BG12" t="s">
         <v>127</v>
       </c>
       <c r="BH12" t="str">
         <f t="shared" si="7"/>
-        <v>MTKNBN20D20A256A</v>
+        <v>MTKNBN20D20A667A</v>
       </c>
     </row>
     <row r="13" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
@@ -1783,27 +1786,27 @@
         <v>124</v>
       </c>
       <c r="AX13">
-        <v>40177</v>
+        <v>34597</v>
       </c>
       <c r="AY13" t="s">
         <v>125</v>
       </c>
       <c r="AZ13" t="str">
         <f t="shared" si="6"/>
-        <v>AB40177JC</v>
+        <v>AB34597JC</v>
       </c>
       <c r="BD13" s="32" t="s">
         <v>126</v>
       </c>
       <c r="BE13">
-        <v>525</v>
+        <v>733</v>
       </c>
       <c r="BG13" t="s">
         <v>127</v>
       </c>
       <c r="BH13" t="str">
         <f t="shared" si="7"/>
-        <v>MTKBNN10D10A525A</v>
+        <v>MTKBNN10D10A733A</v>
       </c>
     </row>
     <row r="14" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
@@ -1812,27 +1815,27 @@
         <v>128</v>
       </c>
       <c r="AX14">
-        <v>16837</v>
+        <v>56214</v>
       </c>
       <c r="AY14" t="s">
         <v>129</v>
       </c>
       <c r="AZ14" t="str">
         <f t="shared" si="6"/>
-        <v>BA16837CJ</v>
+        <v>BA56214CJ</v>
       </c>
       <c r="BD14" s="32" t="s">
         <v>130</v>
       </c>
       <c r="BE14">
-        <v>562</v>
+        <v>497</v>
       </c>
       <c r="BG14" t="s">
         <v>127</v>
       </c>
       <c r="BH14" t="str">
         <f t="shared" si="7"/>
-        <v>MTKNBN20D20A562A</v>
+        <v>MTKNBN20D20A497A</v>
       </c>
     </row>
     <row r="15" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
@@ -1841,27 +1844,27 @@
         <v>124</v>
       </c>
       <c r="AX15">
-        <v>24723</v>
+        <v>85248</v>
       </c>
       <c r="AY15" t="s">
         <v>125</v>
       </c>
       <c r="AZ15" t="str">
         <f t="shared" si="6"/>
-        <v>AB24723JC</v>
+        <v>AB85248JC</v>
       </c>
       <c r="BD15" s="32" t="s">
         <v>126</v>
       </c>
       <c r="BE15">
-        <v>927</v>
+        <v>293</v>
       </c>
       <c r="BG15" t="s">
         <v>127</v>
       </c>
       <c r="BH15" t="str">
         <f t="shared" si="7"/>
-        <v>MTKBNN10D10A927A</v>
+        <v>MTKBNN10D10A293A</v>
       </c>
     </row>
     <row r="16" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
@@ -1870,27 +1873,27 @@
         <v>128</v>
       </c>
       <c r="AX16">
-        <v>62926</v>
+        <v>56839</v>
       </c>
       <c r="AY16" t="s">
         <v>129</v>
       </c>
       <c r="AZ16" t="str">
         <f t="shared" si="6"/>
-        <v>BA62926CJ</v>
+        <v>BA56839CJ</v>
       </c>
       <c r="BD16" s="32" t="s">
         <v>130</v>
       </c>
       <c r="BE16">
-        <v>876</v>
+        <v>571</v>
       </c>
       <c r="BG16" t="s">
         <v>127</v>
       </c>
       <c r="BH16" t="str">
         <f t="shared" si="7"/>
-        <v>MTKNBN20D20A876A</v>
+        <v>MTKNBN20D20A571A</v>
       </c>
     </row>
     <row r="17" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
@@ -1899,27 +1902,27 @@
         <v>124</v>
       </c>
       <c r="AX17">
-        <v>59916</v>
+        <v>46787</v>
       </c>
       <c r="AY17" t="s">
         <v>125</v>
       </c>
       <c r="AZ17" t="str">
         <f t="shared" si="6"/>
-        <v>AB59916JC</v>
+        <v>AB46787JC</v>
       </c>
       <c r="BD17" s="32" t="s">
         <v>126</v>
       </c>
       <c r="BE17">
-        <v>235</v>
+        <v>267</v>
       </c>
       <c r="BG17" t="s">
         <v>127</v>
       </c>
       <c r="BH17" t="str">
         <f t="shared" si="7"/>
-        <v>MTKBNN10D10A235A</v>
+        <v>MTKBNN10D10A267A</v>
       </c>
     </row>
     <row r="18" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
@@ -1928,27 +1931,27 @@
         <v>128</v>
       </c>
       <c r="AX18">
-        <v>98951</v>
+        <v>71887</v>
       </c>
       <c r="AY18" t="s">
         <v>129</v>
       </c>
       <c r="AZ18" t="str">
         <f t="shared" si="6"/>
-        <v>BA98951CJ</v>
+        <v>BA71887CJ</v>
       </c>
       <c r="BD18" s="32" t="s">
         <v>130</v>
       </c>
       <c r="BE18">
-        <v>363</v>
+        <v>483</v>
       </c>
       <c r="BG18" t="s">
         <v>127</v>
       </c>
       <c r="BH18" t="str">
         <f t="shared" si="7"/>
-        <v>MTKNBN20D20A363A</v>
+        <v>MTKNBN20D20A483A</v>
       </c>
     </row>
     <row r="19" ht="14.5" customHeight="1" spans="49:60" x14ac:dyDescent="0.25">
@@ -1956,27 +1959,27 @@
         <v>124</v>
       </c>
       <c r="AX19">
-        <v>62936</v>
+        <v>68590</v>
       </c>
       <c r="AY19" t="s">
         <v>125</v>
       </c>
       <c r="AZ19" t="str">
         <f t="shared" si="6"/>
-        <v>AB62936JC</v>
+        <v>AB68590JC</v>
       </c>
       <c r="BD19" s="32" t="s">
         <v>126</v>
       </c>
       <c r="BE19">
-        <v>274</v>
+        <v>388</v>
       </c>
       <c r="BG19" t="s">
         <v>127</v>
       </c>
       <c r="BH19" t="str">
         <f t="shared" si="7"/>
-        <v>MTKBNN10D10A274A</v>
+        <v>MTKBNN10D10A388A</v>
       </c>
     </row>
     <row r="20" ht="14.5" customHeight="1" spans="49:60" x14ac:dyDescent="0.25">
@@ -1984,27 +1987,27 @@
         <v>128</v>
       </c>
       <c r="AX20">
-        <v>22349</v>
+        <v>64974</v>
       </c>
       <c r="AY20" t="s">
         <v>129</v>
       </c>
       <c r="AZ20" t="str">
         <f t="shared" si="6"/>
-        <v>BA22349CJ</v>
+        <v>BA64974CJ</v>
       </c>
       <c r="BD20" s="32" t="s">
         <v>130</v>
       </c>
       <c r="BE20">
-        <v>892</v>
+        <v>647</v>
       </c>
       <c r="BG20" t="s">
         <v>127</v>
       </c>
       <c r="BH20" t="str">
         <f t="shared" si="7"/>
-        <v>MTKNBN20D20A892A</v>
+        <v>MTKNBN20D20A647A</v>
       </c>
     </row>
     <row r="21" ht="14.5" customHeight="1" spans="49:60" x14ac:dyDescent="0.25">
@@ -2012,27 +2015,27 @@
         <v>124</v>
       </c>
       <c r="AX21">
-        <v>90020</v>
+        <v>66834</v>
       </c>
       <c r="AY21" t="s">
         <v>125</v>
       </c>
       <c r="AZ21" t="str">
         <f t="shared" si="6"/>
-        <v>AB90020JC</v>
+        <v>AB66834JC</v>
       </c>
       <c r="BD21" s="32" t="s">
         <v>126</v>
       </c>
       <c r="BE21">
-        <v>251</v>
+        <v>858</v>
       </c>
       <c r="BG21" t="s">
         <v>127</v>
       </c>
       <c r="BH21" t="str">
         <f t="shared" si="7"/>
-        <v>MTKBNN10D10A251A</v>
+        <v>MTKBNN10D10A858A</v>
       </c>
     </row>
     <row r="22" ht="14.5" customHeight="1" spans="49:60" x14ac:dyDescent="0.25">
@@ -2040,27 +2043,27 @@
         <v>128</v>
       </c>
       <c r="AX22">
-        <v>93643</v>
+        <v>16746</v>
       </c>
       <c r="AY22" t="s">
         <v>129</v>
       </c>
       <c r="AZ22" t="str">
         <f t="shared" si="6"/>
-        <v>BA93643CJ</v>
+        <v>BA16746CJ</v>
       </c>
       <c r="BD22" s="32" t="s">
         <v>130</v>
       </c>
       <c r="BE22">
-        <v>992</v>
+        <v>782</v>
       </c>
       <c r="BG22" t="s">
         <v>127</v>
       </c>
       <c r="BH22" t="str">
         <f t="shared" si="7"/>
-        <v>MTKNBN20D20A992A</v>
+        <v>MTKNBN20D20A782A</v>
       </c>
     </row>
     <row r="23" ht="14.5" customHeight="1" spans="49:60" x14ac:dyDescent="0.25">
@@ -2068,27 +2071,27 @@
         <v>124</v>
       </c>
       <c r="AX23">
-        <v>79028</v>
+        <v>64113</v>
       </c>
       <c r="AY23" t="s">
         <v>125</v>
       </c>
       <c r="AZ23" t="str">
         <f t="shared" si="6"/>
-        <v>AB79028JC</v>
+        <v>AB64113JC</v>
       </c>
       <c r="BD23" s="32" t="s">
         <v>126</v>
       </c>
       <c r="BE23">
-        <v>155</v>
+        <v>440</v>
       </c>
       <c r="BG23" t="s">
         <v>127</v>
       </c>
       <c r="BH23" t="str">
         <f t="shared" si="7"/>
-        <v>MTKBNN10D10A155A</v>
+        <v>MTKBNN10D10A440A</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Hires/Workday_NewHire_Italy_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_Italy_Regression_PK17.xlsx
@@ -1,20 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{F706DC4D-A627-4F02-8DE5-7222689E8301}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="129">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -220,15 +235,6 @@
     <t>Test_1</t>
   </si>
   <si>
-    <t xml:space="preserve">Test failed for 'Lia Davis' Employee:{10699680}TimeoutError: locator.click: Timeout 30000ms exceeded.
-Call log:
-  [2m- waiting for locator('text=Assign Paygroup for Payroll: Lia Davis')[22m
-</t>
-  </si>
-  <si>
-    <t>Failed</t>
-  </si>
-  <si>
     <t>275 Recruitment (Zojez Vizyzi (10279378))</t>
   </si>
   <si>
@@ -238,10 +244,10 @@
     <t>Mr</t>
   </si>
   <si>
-    <t>Lia</t>
-  </si>
-  <si>
-    <t>Davis</t>
+    <t>Blair</t>
+  </si>
+  <si>
+    <t>Kling</t>
   </si>
   <si>
     <t>067898707</t>
@@ -362,113 +368,113 @@
     <t>Test_2</t>
   </si>
   <si>
+    <t>275 Store Management (Gyzag Hopope (10144587))</t>
+  </si>
+  <si>
+    <t>Sydni</t>
+  </si>
+  <si>
+    <t>Heller</t>
+  </si>
+  <si>
+    <t>Auto 90898336</t>
+  </si>
+  <si>
+    <t>Assistant Manager</t>
+  </si>
+  <si>
+    <t>92 Retail Management</t>
+  </si>
+  <si>
+    <t>251 Management Retail</t>
+  </si>
+  <si>
+    <t>Impiegato</t>
+  </si>
+  <si>
+    <t>Level 2</t>
+  </si>
+  <si>
+    <t>AB</t>
+  </si>
+  <si>
+    <t>JC</t>
+  </si>
+  <si>
+    <t>MTKBNN10D10A</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>BA</t>
+  </si>
+  <si>
+    <t>CJ</t>
+  </si>
+  <si>
+    <t>MTKNBN20D20A</t>
+  </si>
+  <si>
     <t>Passed</t>
-  </si>
-  <si>
-    <t>275 Store Management (Gyzag Hopope (10144587))</t>
-  </si>
-  <si>
-    <t>Mia</t>
-  </si>
-  <si>
-    <t>Doyle</t>
-  </si>
-  <si>
-    <t>Auto 4876895</t>
-  </si>
-  <si>
-    <t>Assistant Manager</t>
-  </si>
-  <si>
-    <t>92 Retail Management</t>
-  </si>
-  <si>
-    <t>251 Management Retail</t>
-  </si>
-  <si>
-    <t>Impiegato</t>
-  </si>
-  <si>
-    <t>Level 2</t>
-  </si>
-  <si>
-    <t>AB</t>
-  </si>
-  <si>
-    <t>JC</t>
-  </si>
-  <si>
-    <t>MTKBNN10D10A</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>BA</t>
-  </si>
-  <si>
-    <t>CJ</t>
-  </si>
-  <si>
-    <t>MTKNBN20D20A</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="9" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="14"/>
       <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="14"/>
-      <name val="Arial"/>
     </font>
     <font>
       <u/>
+      <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF4A4A4A"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <color rgb="FF4A4A4A"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <family val="2"/>
-      <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="7">
@@ -480,13 +486,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.5999938962981048"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.1499984740745262"/>
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -503,7 +509,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.7999816888943144"/>
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -523,22 +529,40 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -556,7 +580,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -641,6 +665,10 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
@@ -931,9 +959,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BR23"/>
-  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="65.90625" customWidth="1"/>
@@ -993,7 +1021,7 @@
     <col min="70" max="70" width="39.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" spans="1:70" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:70" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1205,99 +1233,99 @@
         <v>66</v>
       </c>
     </row>
-    <row r="2" ht="14.5" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>67</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="8">
+        <v>10699758</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="D2" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="E2" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="F2" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="G2" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="H2" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="I2" t="s">
         <v>73</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="J2" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="J2" s="15" t="s">
+      <c r="L2" s="16">
+        <f t="shared" ref="L2:L3" ca="1" si="0">TODAY()-31</f>
+        <v>45796</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="N2" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="K2" s="15" t="s">
+      <c r="O2" s="17" t="s">
         <v>77</v>
-      </c>
-      <c r="L2" s="16">
-        <f t="shared" ref="L2:L3" si="0">TODAY()-31</f>
-        <v>45788</v>
-      </c>
-      <c r="M2" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="N2" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="O2" s="17" t="s">
-        <v>79</v>
       </c>
       <c r="P2" s="17">
         <v>1</v>
       </c>
       <c r="Q2" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="R2" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="S2" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="T2" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="R2" s="15" t="s">
+      <c r="U2" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="S2" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="T2" s="18" t="s">
+      <c r="V2" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="W2" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="U2" s="19" t="s">
+      <c r="X2" s="20">
+        <f t="shared" ref="X2:X3" ca="1" si="1">L2</f>
+        <v>45796</v>
+      </c>
+      <c r="Y2" s="16">
+        <f t="shared" ref="Y2:Y3" ca="1" si="2">TODAY()+20</f>
+        <v>45847</v>
+      </c>
+      <c r="Z2" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="V2" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="W2" s="15" t="s">
+      <c r="AA2" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="X2" s="20">
-        <f t="shared" ref="X2:X3" si="1">L2</f>
-        <v>45788</v>
-      </c>
-      <c r="Y2" s="16">
-        <f t="shared" ref="Y2:Y3" si="2">TODAY()+20</f>
-        <v>45839</v>
-      </c>
-      <c r="Z2" s="15" t="s">
+      <c r="AB2" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="AA2" s="21" t="s">
+      <c r="AC2" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="AB2" s="22" t="s">
+      <c r="AD2" s="22" t="s">
         <v>87</v>
-      </c>
-      <c r="AC2" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="AD2" s="22" t="s">
-        <v>89</v>
       </c>
       <c r="AE2" s="11">
         <v>275</v>
@@ -1309,215 +1337,215 @@
         <v>40</v>
       </c>
       <c r="AH2" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AJ2" s="26" t="s">
         <v>90</v>
       </c>
-      <c r="AI2" t="s">
+      <c r="AK2" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="AJ2" s="26" t="s">
+      <c r="AL2" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="AK2" s="15" t="s">
+      <c r="AM2" t="s">
         <v>93</v>
       </c>
-      <c r="AL2" s="15" t="s">
+      <c r="AN2" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="AM2" t="s">
+      <c r="AO2" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="AN2" s="15" t="s">
+      <c r="AP2" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="AO2" s="15" t="s">
+      <c r="AQ2" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="AP2" s="15" t="s">
+      <c r="AR2" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="AS2" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="AQ2" s="27" t="s">
+      <c r="AT2" s="18">
+        <f t="shared" ref="AT2:AT3" ca="1" si="3">X2-1</f>
+        <v>45795</v>
+      </c>
+      <c r="AU2" s="18">
+        <f t="shared" ref="AU2:AU3" ca="1" si="4">X2-1</f>
+        <v>45795</v>
+      </c>
+      <c r="AV2" s="29" t="str">
+        <f t="shared" ref="AV2:AV3" si="5">AJ2</f>
+        <v>N/A</v>
+      </c>
+      <c r="AW2" s="30" t="s">
+        <v>90</v>
+      </c>
+      <c r="AX2" s="30" t="s">
+        <v>90</v>
+      </c>
+      <c r="AY2" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="AZ2" s="31" t="s">
         <v>99</v>
       </c>
-      <c r="AR2" s="22" t="s">
-        <v>92</v>
-      </c>
-      <c r="AS2" s="28" t="s">
+      <c r="BA2" s="32" t="str">
+        <f ca="1">AZ9</f>
+        <v>AB73464JC</v>
+      </c>
+      <c r="BB2" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="BC2" s="31" t="s">
         <v>100</v>
       </c>
-      <c r="AT2" s="18">
-        <f t="shared" ref="AT2:AT3" si="3">X2-1</f>
-        <v>45787</v>
-      </c>
-      <c r="AU2" s="18">
-        <f t="shared" ref="AU2:AU3" si="4">X2-1</f>
-        <v>45787</v>
-      </c>
-      <c r="AV2" s="29">
-        <f t="shared" ref="AV2:AV3" si="5">AJ2</f>
-        <v>NaN</v>
-      </c>
-      <c r="AW2" s="30" t="s">
-        <v>92</v>
-      </c>
-      <c r="AX2" s="30" t="s">
-        <v>92</v>
-      </c>
-      <c r="AY2" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="AZ2" s="31" t="s">
+      <c r="BD2" s="33" t="str">
+        <f ca="1">BH9</f>
+        <v>MTKBNN10D10A236A</v>
+      </c>
+      <c r="BE2" t="s">
         <v>101</v>
       </c>
-      <c r="BA2" s="31">
-        <f>AZ9</f>
-        <v>NaN</v>
-      </c>
-      <c r="BB2" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="BC2" s="31" t="s">
+      <c r="BF2" s="34">
+        <v>35591</v>
+      </c>
+      <c r="BG2" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH2" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="BD2" s="32" t="str">
-        <f>BH9</f>
-        <v>MTKBNN10D10A183A</v>
-      </c>
-      <c r="BE2" t="s">
+      <c r="BI2" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="BJ2" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="BF2" s="33">
-        <v>35591</v>
-      </c>
-      <c r="BG2" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="BH2" s="11" t="s">
+      <c r="BK2" s="34" t="s">
         <v>104</v>
       </c>
-      <c r="BI2" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="BJ2" s="11" t="s">
+      <c r="BL2" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="BM2" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="BK2" s="33" t="s">
+      <c r="BN2" s="31" t="s">
         <v>106</v>
       </c>
-      <c r="BL2" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="BM2" s="11" t="s">
+      <c r="BO2" s="31" t="s">
         <v>107</v>
       </c>
-      <c r="BN2" s="31" t="s">
+      <c r="BP2" s="31" t="s">
         <v>108</v>
       </c>
-      <c r="BO2" s="31" t="s">
+      <c r="BQ2" s="31" t="s">
         <v>109</v>
       </c>
-      <c r="BP2" s="31" t="s">
+      <c r="BR2" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="BQ2" s="31" t="s">
+    </row>
+    <row r="3" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
         <v>111</v>
       </c>
-      <c r="BR2" s="15" t="s">
+      <c r="B3" s="8">
+        <v>10699742</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="D3" s="10" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="3" ht="14.5" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="E3" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="G3" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="B3" s="8">
-        <v>10699677</v>
-      </c>
-      <c r="C3" s="9" t="s">
+      <c r="H3" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="D3" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="G3" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="H3" s="14" t="s">
-        <v>117</v>
-      </c>
       <c r="I3" t="s">
+        <v>73</v>
+      </c>
+      <c r="J3" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="K3" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="J3" s="15" t="s">
+      <c r="L3" s="16">
+        <f t="shared" ca="1" si="0"/>
+        <v>45796</v>
+      </c>
+      <c r="M3" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="N3" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="K3" s="15" t="s">
+      <c r="O3" s="17" t="s">
         <v>77</v>
-      </c>
-      <c r="L3" s="16">
-        <f t="shared" si="0"/>
-        <v>45788</v>
-      </c>
-      <c r="M3" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="N3" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="O3" s="17" t="s">
-        <v>79</v>
       </c>
       <c r="P3" s="17">
         <v>1</v>
       </c>
       <c r="Q3" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="R3" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="S3" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="T3" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="R3" s="15" t="s">
+      <c r="U3" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="S3" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="T3" s="18" t="s">
+      <c r="V3" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="W3" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="U3" s="19" t="s">
+      <c r="X3" s="20">
+        <f t="shared" ca="1" si="1"/>
+        <v>45796</v>
+      </c>
+      <c r="Y3" s="16">
+        <f t="shared" ca="1" si="2"/>
+        <v>45847</v>
+      </c>
+      <c r="Z3" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="V3" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="W3" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="X3" s="20">
-        <f t="shared" si="1"/>
-        <v>45788</v>
-      </c>
-      <c r="Y3" s="16">
-        <f t="shared" si="2"/>
-        <v>45839</v>
-      </c>
-      <c r="Z3" s="15" t="s">
+      <c r="AA3" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="AB3" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="AA3" s="21" t="s">
-        <v>118</v>
-      </c>
-      <c r="AB3" s="22" t="s">
+      <c r="AC3" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="AD3" s="22" t="s">
         <v>87</v>
-      </c>
-      <c r="AC3" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="AD3" s="22" t="s">
-        <v>89</v>
       </c>
       <c r="AE3" s="11">
         <v>275</v>
@@ -1529,600 +1557,613 @@
         <v>40</v>
       </c>
       <c r="AH3" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>89</v>
+      </c>
+      <c r="AJ3" s="26" t="s">
         <v>90</v>
       </c>
-      <c r="AI3" t="s">
+      <c r="AK3" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="AJ3" s="26" t="s">
-        <v>92</v>
-      </c>
-      <c r="AK3" s="15" t="s">
-        <v>93</v>
-      </c>
       <c r="AL3" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AN3" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="AO3" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="AP3" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="AM3" t="s">
-        <v>121</v>
-      </c>
-      <c r="AN3" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="AO3" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="AP3" s="15" t="s">
-        <v>123</v>
-      </c>
       <c r="AQ3" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="AR3" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="AS3" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="AT3" s="18">
+        <f t="shared" ca="1" si="3"/>
+        <v>45795</v>
+      </c>
+      <c r="AU3" s="18">
+        <f t="shared" ca="1" si="4"/>
+        <v>45795</v>
+      </c>
+      <c r="AV3" s="29" t="str">
+        <f t="shared" si="5"/>
+        <v>N/A</v>
+      </c>
+      <c r="AW3" s="30" t="s">
+        <v>90</v>
+      </c>
+      <c r="AX3" s="30" t="s">
+        <v>90</v>
+      </c>
+      <c r="AY3" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="AZ3" s="31" t="s">
         <v>99</v>
       </c>
-      <c r="AR3" s="22" t="s">
-        <v>92</v>
-      </c>
-      <c r="AS3" s="28" t="s">
+      <c r="BA3" s="32" t="str">
+        <f ca="1">AZ10</f>
+        <v>BA59596CJ</v>
+      </c>
+      <c r="BB3" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="BC3" s="31" t="s">
         <v>100</v>
       </c>
-      <c r="AT3" s="18">
-        <f t="shared" si="3"/>
-        <v>45787</v>
-      </c>
-      <c r="AU3" s="18">
-        <f t="shared" si="4"/>
-        <v>45787</v>
-      </c>
-      <c r="AV3" s="29">
-        <f t="shared" si="5"/>
-        <v>NaN</v>
-      </c>
-      <c r="AW3" s="30" t="s">
-        <v>92</v>
-      </c>
-      <c r="AX3" s="30" t="s">
-        <v>92</v>
-      </c>
-      <c r="AY3" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="AZ3" s="31" t="s">
+      <c r="BD3" s="33" t="str">
+        <f ca="1">BH10</f>
+        <v>MTKNBN20D20A714A</v>
+      </c>
+      <c r="BE3" t="s">
         <v>101</v>
       </c>
-      <c r="BA3" s="31">
-        <f>AZ10</f>
-        <v>NaN</v>
-      </c>
-      <c r="BB3" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="BC3" s="31" t="s">
+      <c r="BF3" s="34">
+        <v>35591</v>
+      </c>
+      <c r="BG3" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH3" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="BD3" s="32" t="str">
-        <f>BH10</f>
-        <v>MTKNBN20D20A562A</v>
-      </c>
-      <c r="BE3" t="s">
+      <c r="BI3" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="BJ3" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="BF3" s="33">
-        <v>35591</v>
-      </c>
-      <c r="BG3" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="BH3" s="11" t="s">
+      <c r="BK3" s="34" t="s">
         <v>104</v>
       </c>
-      <c r="BI3" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="BJ3" s="11" t="s">
+      <c r="BL3" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="BM3" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="BK3" s="33" t="s">
+      <c r="BN3" s="31" t="s">
         <v>106</v>
       </c>
-      <c r="BL3" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="BM3" s="11" t="s">
+      <c r="BO3" s="31" t="s">
         <v>107</v>
       </c>
-      <c r="BN3" s="31" t="s">
+      <c r="BP3" s="31" t="s">
         <v>108</v>
       </c>
-      <c r="BO3" s="31" t="s">
+      <c r="BQ3" s="31" t="s">
         <v>109</v>
       </c>
-      <c r="BP3" s="31" t="s">
+      <c r="BR3" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="BQ3" s="31" t="s">
-        <v>111</v>
-      </c>
-      <c r="BR3" s="15" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="4" spans="3:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:70" x14ac:dyDescent="0.35">
       <c r="C4" s="9"/>
       <c r="AZ4" s="7"/>
-      <c r="BA4" s="34"/>
-    </row>
-    <row r="5" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="BA4" s="35"/>
+    </row>
+    <row r="5" spans="1:70" x14ac:dyDescent="0.25">
       <c r="C5" s="9"/>
     </row>
-    <row r="6" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:70" x14ac:dyDescent="0.25">
       <c r="C6" s="9"/>
     </row>
-    <row r="7" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:70" x14ac:dyDescent="0.25">
       <c r="C7" s="9"/>
     </row>
-    <row r="8" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:70" x14ac:dyDescent="0.25">
       <c r="C8" s="9"/>
     </row>
-    <row r="9" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C9" s="9"/>
       <c r="AW9" t="s">
+        <v>121</v>
+      </c>
+      <c r="AX9">
+        <f t="array" aca="1" ref="AX9:AX23" ca="1">_xlfn.RANDARRAY(15,1,12345,99999,TRUE)</f>
+        <v>73464</v>
+      </c>
+      <c r="AY9" t="s">
+        <v>122</v>
+      </c>
+      <c r="AZ9" t="str">
+        <f ca="1">AW9&amp;AX9&amp;AY9</f>
+        <v>AB73464JC</v>
+      </c>
+      <c r="BD9" s="33" t="s">
+        <v>123</v>
+      </c>
+      <c r="BE9">
+        <f t="array" aca="1" ref="BE9:BE23" ca="1">_xlfn.RANDARRAY(15,1,123,999,TRUE)</f>
+        <v>236</v>
+      </c>
+      <c r="BG9" t="s">
         <v>124</v>
       </c>
-      <c r="AX9">
-        <f t="array" ref="AX9:AX23">_xlfn.RANDARRAY(15,1,12345,99999,TRUE)</f>
-        <v>87517</v>
-      </c>
-      <c r="AY9" t="s">
-        <v>125</v>
-      </c>
-      <c r="AZ9" t="str">
-        <f>AW9&amp;AX9&amp;AY9</f>
-        <v>AB87517JC</v>
-      </c>
-      <c r="BD9" s="32" t="s">
-        <v>126</v>
-      </c>
-      <c r="BE9">
-        <f t="array" ref="BE9:BE23">_xlfn.RANDARRAY(15,1,123,999,TRUE)</f>
-        <v>183</v>
-      </c>
-      <c r="BG9" t="s">
-        <v>127</v>
-      </c>
       <c r="BH9" t="str">
-        <f>BD9&amp;BE9&amp;BF9&amp;BG9</f>
-        <v>MTKBNN10D10A183A</v>
-      </c>
-    </row>
-    <row r="10" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
+        <f ca="1">BD9&amp;BE9&amp;BF9&amp;BG9</f>
+        <v>MTKBNN10D10A236A</v>
+      </c>
+    </row>
+    <row r="10" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C10" s="9"/>
       <c r="AW10" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="AX10">
-        <v>18396</v>
+        <f ca="1"/>
+        <v>59596</v>
       </c>
       <c r="AY10" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="AZ10" t="str">
-        <f t="shared" ref="AZ10:AZ23" si="6">AW10&amp;AX10&amp;AY10</f>
-        <v>BA18396CJ</v>
-      </c>
-      <c r="BD10" s="32" t="s">
-        <v>130</v>
+        <f t="shared" ref="AZ10:AZ23" ca="1" si="6">AW10&amp;AX10&amp;AY10</f>
+        <v>BA59596CJ</v>
+      </c>
+      <c r="BD10" s="33" t="s">
+        <v>127</v>
       </c>
       <c r="BE10">
-        <v>562</v>
+        <f ca="1"/>
+        <v>714</v>
       </c>
       <c r="BG10" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="BH10" t="str">
-        <f t="shared" ref="BH10:BH23" si="7">BD10&amp;BE10&amp;BF10&amp;BG10</f>
-        <v>MTKNBN20D20A562A</v>
-      </c>
-    </row>
-    <row r="11" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
+        <f t="shared" ref="BH10:BH23" ca="1" si="7">BD10&amp;BE10&amp;BF10&amp;BG10</f>
+        <v>MTKNBN20D20A714A</v>
+      </c>
+    </row>
+    <row r="11" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C11" s="9"/>
       <c r="AW11" t="s">
+        <v>121</v>
+      </c>
+      <c r="AX11">
+        <f ca="1"/>
+        <v>39139</v>
+      </c>
+      <c r="AY11" t="s">
+        <v>122</v>
+      </c>
+      <c r="AZ11" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v>AB39139JC</v>
+      </c>
+      <c r="BD11" s="33" t="s">
+        <v>123</v>
+      </c>
+      <c r="BE11">
+        <f ca="1"/>
+        <v>338</v>
+      </c>
+      <c r="BG11" t="s">
         <v>124</v>
       </c>
-      <c r="AX11">
-        <v>90133</v>
-      </c>
-      <c r="AY11" t="s">
-        <v>125</v>
-      </c>
-      <c r="AZ11" t="str">
-        <f t="shared" si="6"/>
-        <v>AB90133JC</v>
-      </c>
-      <c r="BD11" s="32" t="s">
-        <v>126</v>
-      </c>
-      <c r="BE11">
-        <v>196</v>
-      </c>
-      <c r="BG11" t="s">
-        <v>127</v>
-      </c>
       <c r="BH11" t="str">
-        <f t="shared" si="7"/>
-        <v>MTKBNN10D10A196A</v>
-      </c>
-    </row>
-    <row r="12" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>MTKBNN10D10A338A</v>
+      </c>
+    </row>
+    <row r="12" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C12" s="9"/>
       <c r="AW12" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="AX12">
-        <v>54714</v>
+        <f ca="1"/>
+        <v>58206</v>
       </c>
       <c r="AY12" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="AZ12" t="str">
-        <f t="shared" si="6"/>
-        <v>BA54714CJ</v>
-      </c>
-      <c r="BD12" s="32" t="s">
-        <v>130</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>BA58206CJ</v>
+      </c>
+      <c r="BD12" s="33" t="s">
+        <v>127</v>
       </c>
       <c r="BE12">
-        <v>667</v>
+        <f ca="1"/>
+        <v>283</v>
       </c>
       <c r="BG12" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="BH12" t="str">
-        <f t="shared" si="7"/>
-        <v>MTKNBN20D20A667A</v>
-      </c>
-    </row>
-    <row r="13" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>MTKNBN20D20A283A</v>
+      </c>
+    </row>
+    <row r="13" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C13" s="9"/>
       <c r="AW13" t="s">
+        <v>121</v>
+      </c>
+      <c r="AX13">
+        <f ca="1"/>
+        <v>78907</v>
+      </c>
+      <c r="AY13" t="s">
+        <v>122</v>
+      </c>
+      <c r="AZ13" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v>AB78907JC</v>
+      </c>
+      <c r="BD13" s="33" t="s">
+        <v>123</v>
+      </c>
+      <c r="BE13">
+        <f ca="1"/>
+        <v>511</v>
+      </c>
+      <c r="BG13" t="s">
         <v>124</v>
       </c>
-      <c r="AX13">
-        <v>34597</v>
-      </c>
-      <c r="AY13" t="s">
-        <v>125</v>
-      </c>
-      <c r="AZ13" t="str">
-        <f t="shared" si="6"/>
-        <v>AB34597JC</v>
-      </c>
-      <c r="BD13" s="32" t="s">
-        <v>126</v>
-      </c>
-      <c r="BE13">
-        <v>733</v>
-      </c>
-      <c r="BG13" t="s">
-        <v>127</v>
-      </c>
       <c r="BH13" t="str">
-        <f t="shared" si="7"/>
-        <v>MTKBNN10D10A733A</v>
-      </c>
-    </row>
-    <row r="14" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>MTKBNN10D10A511A</v>
+      </c>
+    </row>
+    <row r="14" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C14" s="9"/>
       <c r="AW14" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="AX14">
-        <v>56214</v>
+        <f ca="1"/>
+        <v>75301</v>
       </c>
       <c r="AY14" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="AZ14" t="str">
-        <f t="shared" si="6"/>
-        <v>BA56214CJ</v>
-      </c>
-      <c r="BD14" s="32" t="s">
-        <v>130</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>BA75301CJ</v>
+      </c>
+      <c r="BD14" s="33" t="s">
+        <v>127</v>
       </c>
       <c r="BE14">
-        <v>497</v>
+        <f ca="1"/>
+        <v>193</v>
       </c>
       <c r="BG14" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="BH14" t="str">
-        <f t="shared" si="7"/>
-        <v>MTKNBN20D20A497A</v>
-      </c>
-    </row>
-    <row r="15" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>MTKNBN20D20A193A</v>
+      </c>
+    </row>
+    <row r="15" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C15" s="9"/>
       <c r="AW15" t="s">
+        <v>121</v>
+      </c>
+      <c r="AX15">
+        <f ca="1"/>
+        <v>26947</v>
+      </c>
+      <c r="AY15" t="s">
+        <v>122</v>
+      </c>
+      <c r="AZ15" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v>AB26947JC</v>
+      </c>
+      <c r="BD15" s="33" t="s">
+        <v>123</v>
+      </c>
+      <c r="BE15">
+        <f ca="1"/>
+        <v>790</v>
+      </c>
+      <c r="BG15" t="s">
         <v>124</v>
       </c>
-      <c r="AX15">
-        <v>85248</v>
-      </c>
-      <c r="AY15" t="s">
-        <v>125</v>
-      </c>
-      <c r="AZ15" t="str">
-        <f t="shared" si="6"/>
-        <v>AB85248JC</v>
-      </c>
-      <c r="BD15" s="32" t="s">
-        <v>126</v>
-      </c>
-      <c r="BE15">
-        <v>293</v>
-      </c>
-      <c r="BG15" t="s">
-        <v>127</v>
-      </c>
       <c r="BH15" t="str">
-        <f t="shared" si="7"/>
-        <v>MTKBNN10D10A293A</v>
-      </c>
-    </row>
-    <row r="16" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>MTKBNN10D10A790A</v>
+      </c>
+    </row>
+    <row r="16" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C16" s="9"/>
       <c r="AW16" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="AX16">
-        <v>56839</v>
+        <f ca="1"/>
+        <v>17457</v>
       </c>
       <c r="AY16" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="AZ16" t="str">
-        <f t="shared" si="6"/>
-        <v>BA56839CJ</v>
-      </c>
-      <c r="BD16" s="32" t="s">
-        <v>130</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>BA17457CJ</v>
+      </c>
+      <c r="BD16" s="33" t="s">
+        <v>127</v>
       </c>
       <c r="BE16">
-        <v>571</v>
+        <f ca="1"/>
+        <v>170</v>
       </c>
       <c r="BG16" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="BH16" t="str">
-        <f t="shared" si="7"/>
-        <v>MTKNBN20D20A571A</v>
-      </c>
-    </row>
-    <row r="17" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>MTKNBN20D20A170A</v>
+      </c>
+    </row>
+    <row r="17" spans="3:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C17" s="9"/>
       <c r="AW17" t="s">
+        <v>121</v>
+      </c>
+      <c r="AX17">
+        <f ca="1"/>
+        <v>12612</v>
+      </c>
+      <c r="AY17" t="s">
+        <v>122</v>
+      </c>
+      <c r="AZ17" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v>AB12612JC</v>
+      </c>
+      <c r="BD17" s="33" t="s">
+        <v>123</v>
+      </c>
+      <c r="BE17">
+        <f ca="1"/>
+        <v>844</v>
+      </c>
+      <c r="BG17" t="s">
         <v>124</v>
       </c>
-      <c r="AX17">
-        <v>46787</v>
-      </c>
-      <c r="AY17" t="s">
-        <v>125</v>
-      </c>
-      <c r="AZ17" t="str">
-        <f t="shared" si="6"/>
-        <v>AB46787JC</v>
-      </c>
-      <c r="BD17" s="32" t="s">
-        <v>126</v>
-      </c>
-      <c r="BE17">
-        <v>267</v>
-      </c>
-      <c r="BG17" t="s">
-        <v>127</v>
-      </c>
       <c r="BH17" t="str">
-        <f t="shared" si="7"/>
-        <v>MTKBNN10D10A267A</v>
-      </c>
-    </row>
-    <row r="18" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>MTKBNN10D10A844A</v>
+      </c>
+    </row>
+    <row r="18" spans="3:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C18" s="9"/>
       <c r="AW18" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="AX18">
-        <v>71887</v>
+        <f ca="1"/>
+        <v>99061</v>
       </c>
       <c r="AY18" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="AZ18" t="str">
-        <f t="shared" si="6"/>
-        <v>BA71887CJ</v>
-      </c>
-      <c r="BD18" s="32" t="s">
-        <v>130</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>BA99061CJ</v>
+      </c>
+      <c r="BD18" s="33" t="s">
+        <v>127</v>
       </c>
       <c r="BE18">
-        <v>483</v>
+        <f ca="1"/>
+        <v>568</v>
       </c>
       <c r="BG18" t="s">
+        <v>124</v>
+      </c>
+      <c r="BH18" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v>MTKNBN20D20A568A</v>
+      </c>
+    </row>
+    <row r="19" spans="3:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AW19" t="s">
+        <v>121</v>
+      </c>
+      <c r="AX19">
+        <f ca="1"/>
+        <v>35921</v>
+      </c>
+      <c r="AY19" t="s">
+        <v>122</v>
+      </c>
+      <c r="AZ19" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v>AB35921JC</v>
+      </c>
+      <c r="BD19" s="33" t="s">
+        <v>123</v>
+      </c>
+      <c r="BE19">
+        <f ca="1"/>
+        <v>828</v>
+      </c>
+      <c r="BG19" t="s">
+        <v>124</v>
+      </c>
+      <c r="BH19" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v>MTKBNN10D10A828A</v>
+      </c>
+    </row>
+    <row r="20" spans="3:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AW20" t="s">
+        <v>125</v>
+      </c>
+      <c r="AX20">
+        <f ca="1"/>
+        <v>16806</v>
+      </c>
+      <c r="AY20" t="s">
+        <v>126</v>
+      </c>
+      <c r="AZ20" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v>BA16806CJ</v>
+      </c>
+      <c r="BD20" s="33" t="s">
         <v>127</v>
       </c>
-      <c r="BH18" t="str">
-        <f t="shared" si="7"/>
-        <v>MTKNBN20D20A483A</v>
-      </c>
-    </row>
-    <row r="19" ht="14.5" customHeight="1" spans="49:60" x14ac:dyDescent="0.25">
-      <c r="AW19" t="s">
+      <c r="BE20">
+        <f ca="1"/>
+        <v>503</v>
+      </c>
+      <c r="BG20" t="s">
         <v>124</v>
       </c>
-      <c r="AX19">
-        <v>68590</v>
-      </c>
-      <c r="AY19" t="s">
+      <c r="BH20" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v>MTKNBN20D20A503A</v>
+      </c>
+    </row>
+    <row r="21" spans="3:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AW21" t="s">
+        <v>121</v>
+      </c>
+      <c r="AX21">
+        <f ca="1"/>
+        <v>97825</v>
+      </c>
+      <c r="AY21" t="s">
+        <v>122</v>
+      </c>
+      <c r="AZ21" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v>AB97825JC</v>
+      </c>
+      <c r="BD21" s="33" t="s">
+        <v>123</v>
+      </c>
+      <c r="BE21">
+        <f ca="1"/>
+        <v>605</v>
+      </c>
+      <c r="BG21" t="s">
+        <v>124</v>
+      </c>
+      <c r="BH21" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v>MTKBNN10D10A605A</v>
+      </c>
+    </row>
+    <row r="22" spans="3:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AW22" t="s">
         <v>125</v>
       </c>
-      <c r="AZ19" t="str">
-        <f t="shared" si="6"/>
-        <v>AB68590JC</v>
-      </c>
-      <c r="BD19" s="32" t="s">
+      <c r="AX22">
+        <f ca="1"/>
+        <v>73036</v>
+      </c>
+      <c r="AY22" t="s">
         <v>126</v>
       </c>
-      <c r="BE19">
-        <v>388</v>
-      </c>
-      <c r="BG19" t="s">
+      <c r="AZ22" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v>BA73036CJ</v>
+      </c>
+      <c r="BD22" s="33" t="s">
         <v>127</v>
       </c>
-      <c r="BH19" t="str">
-        <f t="shared" si="7"/>
-        <v>MTKBNN10D10A388A</v>
-      </c>
-    </row>
-    <row r="20" ht="14.5" customHeight="1" spans="49:60" x14ac:dyDescent="0.25">
-      <c r="AW20" t="s">
-        <v>128</v>
-      </c>
-      <c r="AX20">
-        <v>64974</v>
-      </c>
-      <c r="AY20" t="s">
-        <v>129</v>
-      </c>
-      <c r="AZ20" t="str">
-        <f t="shared" si="6"/>
-        <v>BA64974CJ</v>
-      </c>
-      <c r="BD20" s="32" t="s">
-        <v>130</v>
-      </c>
-      <c r="BE20">
-        <v>647</v>
-      </c>
-      <c r="BG20" t="s">
-        <v>127</v>
-      </c>
-      <c r="BH20" t="str">
-        <f t="shared" si="7"/>
-        <v>MTKNBN20D20A647A</v>
-      </c>
-    </row>
-    <row r="21" ht="14.5" customHeight="1" spans="49:60" x14ac:dyDescent="0.25">
-      <c r="AW21" t="s">
+      <c r="BE22">
+        <f ca="1"/>
+        <v>515</v>
+      </c>
+      <c r="BG22" t="s">
         <v>124</v>
       </c>
-      <c r="AX21">
-        <v>66834</v>
-      </c>
-      <c r="AY21" t="s">
-        <v>125</v>
-      </c>
-      <c r="AZ21" t="str">
-        <f t="shared" si="6"/>
-        <v>AB66834JC</v>
-      </c>
-      <c r="BD21" s="32" t="s">
-        <v>126</v>
-      </c>
-      <c r="BE21">
-        <v>858</v>
-      </c>
-      <c r="BG21" t="s">
-        <v>127</v>
-      </c>
-      <c r="BH21" t="str">
-        <f t="shared" si="7"/>
-        <v>MTKBNN10D10A858A</v>
-      </c>
-    </row>
-    <row r="22" ht="14.5" customHeight="1" spans="49:60" x14ac:dyDescent="0.25">
-      <c r="AW22" t="s">
-        <v>128</v>
-      </c>
-      <c r="AX22">
-        <v>16746</v>
-      </c>
-      <c r="AY22" t="s">
-        <v>129</v>
-      </c>
-      <c r="AZ22" t="str">
-        <f t="shared" si="6"/>
-        <v>BA16746CJ</v>
-      </c>
-      <c r="BD22" s="32" t="s">
-        <v>130</v>
-      </c>
-      <c r="BE22">
-        <v>782</v>
-      </c>
-      <c r="BG22" t="s">
-        <v>127</v>
-      </c>
       <c r="BH22" t="str">
-        <f t="shared" si="7"/>
-        <v>MTKNBN20D20A782A</v>
-      </c>
-    </row>
-    <row r="23" ht="14.5" customHeight="1" spans="49:60" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>MTKNBN20D20A515A</v>
+      </c>
+    </row>
+    <row r="23" spans="3:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="AW23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AX23">
+        <f ca="1"/>
+        <v>46268</v>
+      </c>
+      <c r="AY23" t="s">
+        <v>122</v>
+      </c>
+      <c r="AZ23" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v>AB46268JC</v>
+      </c>
+      <c r="BD23" s="33" t="s">
+        <v>123</v>
+      </c>
+      <c r="BE23">
+        <f ca="1"/>
+        <v>654</v>
+      </c>
+      <c r="BG23" t="s">
         <v>124</v>
       </c>
-      <c r="AX23">
-        <v>64113</v>
-      </c>
-      <c r="AY23" t="s">
-        <v>125</v>
-      </c>
-      <c r="AZ23" t="str">
-        <f t="shared" si="6"/>
-        <v>AB64113JC</v>
-      </c>
-      <c r="BD23" s="32" t="s">
-        <v>126</v>
-      </c>
-      <c r="BE23">
-        <v>440</v>
-      </c>
-      <c r="BG23" t="s">
-        <v>127</v>
-      </c>
       <c r="BH23" t="str">
-        <f t="shared" si="7"/>
-        <v>MTKBNN10D10A440A</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>MTKBNN10D10A654A</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AS2:AS3">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BQ2:BQ3">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K3">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S3">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V3">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2:Z3">
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AS2:AS3 Z2:Z3 V2:V3 S2:S3 K2:K3 BQ2:BQ3" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="I2" r:id="rId1"/>
-    <hyperlink ref="U2" r:id="rId2"/>
-    <hyperlink ref="AH2" r:id="rId3"/>
-    <hyperlink ref="I3" r:id="rId4"/>
-    <hyperlink ref="U3" r:id="rId5"/>
+    <hyperlink ref="I2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="U2" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="AH2" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="I3" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="U3" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId6"/>
 </worksheet>
 </file>
--- a/Data/Hires/Workday_NewHire_Italy_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_Italy_Regression_PK17.xlsx
@@ -220,7 +220,7 @@
     <t>Test_1</t>
   </si>
   <si>
-    <t>10700248</t>
+    <t>10700453</t>
   </si>
   <si>
     <t>Passed</t>
@@ -235,10 +235,10 @@
     <t>Mr</t>
   </si>
   <si>
-    <t>Eliseo</t>
-  </si>
-  <si>
-    <t>Mosciski</t>
+    <t>Sheridan</t>
+  </si>
+  <si>
+    <t>Effertz</t>
   </si>
   <si>
     <t>067898707</t>
@@ -359,7 +359,7 @@
     <t>Test_2</t>
   </si>
   <si>
-    <t>10700249</t>
+    <t>10700454</t>
   </si>
   <si>
     <t>275 Store Management (Gyzag Hopope (10144587))</t>
@@ -368,10 +368,10 @@
     <t>Humberto</t>
   </si>
   <si>
-    <t>Hodkiewicz</t>
-  </si>
-  <si>
-    <t>Auto 78628774</t>
+    <t>Lindgren</t>
+  </si>
+  <si>
+    <t>Auto 52365464</t>
   </si>
   <si>
     <t>Assistant Manager</t>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="L2" s="16">
         <f t="shared" ref="L2:L3" si="0">TODAY()-31</f>
-        <v>45821</v>
+        <v>45842</v>
       </c>
       <c r="M2" s="11" t="s">
         <v>71</v>
@@ -1279,11 +1279,11 @@
       </c>
       <c r="X2" s="20">
         <f t="shared" ref="X2:X3" si="1">L2</f>
-        <v>45821</v>
+        <v>45842</v>
       </c>
       <c r="Y2" s="16">
         <f t="shared" ref="Y2:Y3" si="2">TODAY()+20</f>
-        <v>45872</v>
+        <v>45893</v>
       </c>
       <c r="Z2" s="15" t="s">
         <v>85</v>
@@ -1347,11 +1347,11 @@
       </c>
       <c r="AT2" s="18">
         <f t="shared" ref="AT2:AT3" si="3">X2-1</f>
-        <v>45820</v>
+        <v>45841</v>
       </c>
       <c r="AU2" s="18">
         <f t="shared" ref="AU2:AU3" si="4">X2-1</f>
-        <v>45820</v>
+        <v>45841</v>
       </c>
       <c r="AV2" s="29">
         <f t="shared" ref="AV2:AV3" si="5">AJ2</f>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="BD2" s="33" t="str">
         <f>BH9</f>
-        <v>MTKBNN10D10A354A</v>
+        <v>MTKBNN10D10A316A</v>
       </c>
       <c r="BE2" t="s">
         <v>103</v>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="L3" s="16">
         <f t="shared" si="0"/>
-        <v>45821</v>
+        <v>45842</v>
       </c>
       <c r="M3" s="11" t="s">
         <v>71</v>
@@ -1499,11 +1499,11 @@
       </c>
       <c r="X3" s="20">
         <f t="shared" si="1"/>
-        <v>45821</v>
+        <v>45842</v>
       </c>
       <c r="Y3" s="16">
         <f t="shared" si="2"/>
-        <v>45872</v>
+        <v>45893</v>
       </c>
       <c r="Z3" s="15" t="s">
         <v>85</v>
@@ -1567,11 +1567,11 @@
       </c>
       <c r="AT3" s="18">
         <f t="shared" si="3"/>
-        <v>45820</v>
+        <v>45841</v>
       </c>
       <c r="AU3" s="18">
         <f t="shared" si="4"/>
-        <v>45820</v>
+        <v>45841</v>
       </c>
       <c r="AV3" s="29">
         <f t="shared" si="5"/>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="BD3" s="33" t="str">
         <f>BH10</f>
-        <v>MTKNBN20D20A151A</v>
+        <v>MTKNBN20D20A222A</v>
       </c>
       <c r="BE3" t="s">
         <v>103</v>
@@ -1670,28 +1670,28 @@
       </c>
       <c r="AX9">
         <f t="array" ref="AX9:AX23">_xlfn.RANDARRAY(15,1,12345,99999,TRUE)</f>
-        <v>22067</v>
+        <v>71627</v>
       </c>
       <c r="AY9" t="s">
         <v>125</v>
       </c>
       <c r="AZ9" t="str">
         <f>AW9&amp;AX9&amp;AY9</f>
-        <v>AB22067JC</v>
+        <v>AB71627JC</v>
       </c>
       <c r="BD9" s="33" t="s">
         <v>126</v>
       </c>
       <c r="BE9">
         <f t="array" ref="BE9:BE23">_xlfn.RANDARRAY(15,1,123,999,TRUE)</f>
-        <v>354</v>
+        <v>316</v>
       </c>
       <c r="BG9" t="s">
         <v>127</v>
       </c>
       <c r="BH9" t="str">
         <f>BD9&amp;BE9&amp;BF9&amp;BG9</f>
-        <v>MTKBNN10D10A354A</v>
+        <v>MTKBNN10D10A316A</v>
       </c>
     </row>
     <row r="10" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
@@ -1700,27 +1700,27 @@
         <v>128</v>
       </c>
       <c r="AX10">
-        <v>84006</v>
+        <v>24607</v>
       </c>
       <c r="AY10" t="s">
         <v>129</v>
       </c>
       <c r="AZ10" t="str">
         <f t="shared" ref="AZ10:AZ23" si="6">AW10&amp;AX10&amp;AY10</f>
-        <v>BA84006CJ</v>
+        <v>BA24607CJ</v>
       </c>
       <c r="BD10" s="33" t="s">
         <v>130</v>
       </c>
       <c r="BE10">
-        <v>151</v>
+        <v>222</v>
       </c>
       <c r="BG10" t="s">
         <v>127</v>
       </c>
       <c r="BH10" t="str">
         <f t="shared" ref="BH10:BH23" si="7">BD10&amp;BE10&amp;BF10&amp;BG10</f>
-        <v>MTKNBN20D20A151A</v>
+        <v>MTKNBN20D20A222A</v>
       </c>
     </row>
     <row r="11" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
@@ -1729,27 +1729,27 @@
         <v>124</v>
       </c>
       <c r="AX11">
-        <v>77368</v>
+        <v>63188</v>
       </c>
       <c r="AY11" t="s">
         <v>125</v>
       </c>
       <c r="AZ11" t="str">
         <f t="shared" si="6"/>
-        <v>AB77368JC</v>
+        <v>AB63188JC</v>
       </c>
       <c r="BD11" s="33" t="s">
         <v>126</v>
       </c>
       <c r="BE11">
-        <v>891</v>
+        <v>322</v>
       </c>
       <c r="BG11" t="s">
         <v>127</v>
       </c>
       <c r="BH11" t="str">
         <f t="shared" si="7"/>
-        <v>MTKBNN10D10A891A</v>
+        <v>MTKBNN10D10A322A</v>
       </c>
     </row>
     <row r="12" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
@@ -1758,27 +1758,27 @@
         <v>128</v>
       </c>
       <c r="AX12">
-        <v>45760</v>
+        <v>81234</v>
       </c>
       <c r="AY12" t="s">
         <v>129</v>
       </c>
       <c r="AZ12" t="str">
         <f t="shared" si="6"/>
-        <v>BA45760CJ</v>
+        <v>BA81234CJ</v>
       </c>
       <c r="BD12" s="33" t="s">
         <v>130</v>
       </c>
       <c r="BE12">
-        <v>885</v>
+        <v>630</v>
       </c>
       <c r="BG12" t="s">
         <v>127</v>
       </c>
       <c r="BH12" t="str">
         <f t="shared" si="7"/>
-        <v>MTKNBN20D20A885A</v>
+        <v>MTKNBN20D20A630A</v>
       </c>
     </row>
     <row r="13" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
@@ -1787,27 +1787,27 @@
         <v>124</v>
       </c>
       <c r="AX13">
-        <v>27388</v>
+        <v>14440</v>
       </c>
       <c r="AY13" t="s">
         <v>125</v>
       </c>
       <c r="AZ13" t="str">
         <f t="shared" si="6"/>
-        <v>AB27388JC</v>
+        <v>AB14440JC</v>
       </c>
       <c r="BD13" s="33" t="s">
         <v>126</v>
       </c>
       <c r="BE13">
-        <v>381</v>
+        <v>210</v>
       </c>
       <c r="BG13" t="s">
         <v>127</v>
       </c>
       <c r="BH13" t="str">
         <f t="shared" si="7"/>
-        <v>MTKBNN10D10A381A</v>
+        <v>MTKBNN10D10A210A</v>
       </c>
     </row>
     <row r="14" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
@@ -1816,27 +1816,27 @@
         <v>128</v>
       </c>
       <c r="AX14">
-        <v>31844</v>
+        <v>62973</v>
       </c>
       <c r="AY14" t="s">
         <v>129</v>
       </c>
       <c r="AZ14" t="str">
         <f t="shared" si="6"/>
-        <v>BA31844CJ</v>
+        <v>BA62973CJ</v>
       </c>
       <c r="BD14" s="33" t="s">
         <v>130</v>
       </c>
       <c r="BE14">
-        <v>206</v>
+        <v>240</v>
       </c>
       <c r="BG14" t="s">
         <v>127</v>
       </c>
       <c r="BH14" t="str">
         <f t="shared" si="7"/>
-        <v>MTKNBN20D20A206A</v>
+        <v>MTKNBN20D20A240A</v>
       </c>
     </row>
     <row r="15" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
@@ -1845,27 +1845,27 @@
         <v>124</v>
       </c>
       <c r="AX15">
-        <v>49829</v>
+        <v>95116</v>
       </c>
       <c r="AY15" t="s">
         <v>125</v>
       </c>
       <c r="AZ15" t="str">
         <f t="shared" si="6"/>
-        <v>AB49829JC</v>
+        <v>AB95116JC</v>
       </c>
       <c r="BD15" s="33" t="s">
         <v>126</v>
       </c>
       <c r="BE15">
-        <v>180</v>
+        <v>777</v>
       </c>
       <c r="BG15" t="s">
         <v>127</v>
       </c>
       <c r="BH15" t="str">
         <f t="shared" si="7"/>
-        <v>MTKBNN10D10A180A</v>
+        <v>MTKBNN10D10A777A</v>
       </c>
     </row>
     <row r="16" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
@@ -1874,27 +1874,27 @@
         <v>128</v>
       </c>
       <c r="AX16">
-        <v>45309</v>
+        <v>12952</v>
       </c>
       <c r="AY16" t="s">
         <v>129</v>
       </c>
       <c r="AZ16" t="str">
         <f t="shared" si="6"/>
-        <v>BA45309CJ</v>
+        <v>BA12952CJ</v>
       </c>
       <c r="BD16" s="33" t="s">
         <v>130</v>
       </c>
       <c r="BE16">
-        <v>834</v>
+        <v>430</v>
       </c>
       <c r="BG16" t="s">
         <v>127</v>
       </c>
       <c r="BH16" t="str">
         <f t="shared" si="7"/>
-        <v>MTKNBN20D20A834A</v>
+        <v>MTKNBN20D20A430A</v>
       </c>
     </row>
     <row r="17" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
@@ -1903,27 +1903,27 @@
         <v>124</v>
       </c>
       <c r="AX17">
-        <v>33664</v>
+        <v>70143</v>
       </c>
       <c r="AY17" t="s">
         <v>125</v>
       </c>
       <c r="AZ17" t="str">
         <f t="shared" si="6"/>
-        <v>AB33664JC</v>
+        <v>AB70143JC</v>
       </c>
       <c r="BD17" s="33" t="s">
         <v>126</v>
       </c>
       <c r="BE17">
-        <v>261</v>
+        <v>782</v>
       </c>
       <c r="BG17" t="s">
         <v>127</v>
       </c>
       <c r="BH17" t="str">
         <f t="shared" si="7"/>
-        <v>MTKBNN10D10A261A</v>
+        <v>MTKBNN10D10A782A</v>
       </c>
     </row>
     <row r="18" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
@@ -1932,27 +1932,27 @@
         <v>128</v>
       </c>
       <c r="AX18">
-        <v>96141</v>
+        <v>94645</v>
       </c>
       <c r="AY18" t="s">
         <v>129</v>
       </c>
       <c r="AZ18" t="str">
         <f t="shared" si="6"/>
-        <v>BA96141CJ</v>
+        <v>BA94645CJ</v>
       </c>
       <c r="BD18" s="33" t="s">
         <v>130</v>
       </c>
       <c r="BE18">
-        <v>880</v>
+        <v>196</v>
       </c>
       <c r="BG18" t="s">
         <v>127</v>
       </c>
       <c r="BH18" t="str">
         <f t="shared" si="7"/>
-        <v>MTKNBN20D20A880A</v>
+        <v>MTKNBN20D20A196A</v>
       </c>
     </row>
     <row r="19" ht="14.5" customHeight="1" spans="49:60" x14ac:dyDescent="0.25">
@@ -1960,27 +1960,27 @@
         <v>124</v>
       </c>
       <c r="AX19">
-        <v>38903</v>
+        <v>94260</v>
       </c>
       <c r="AY19" t="s">
         <v>125</v>
       </c>
       <c r="AZ19" t="str">
         <f t="shared" si="6"/>
-        <v>AB38903JC</v>
+        <v>AB94260JC</v>
       </c>
       <c r="BD19" s="33" t="s">
         <v>126</v>
       </c>
       <c r="BE19">
-        <v>869</v>
+        <v>759</v>
       </c>
       <c r="BG19" t="s">
         <v>127</v>
       </c>
       <c r="BH19" t="str">
         <f t="shared" si="7"/>
-        <v>MTKBNN10D10A869A</v>
+        <v>MTKBNN10D10A759A</v>
       </c>
     </row>
     <row r="20" ht="14.5" customHeight="1" spans="49:60" x14ac:dyDescent="0.25">
@@ -1988,27 +1988,27 @@
         <v>128</v>
       </c>
       <c r="AX20">
-        <v>42436</v>
+        <v>41818</v>
       </c>
       <c r="AY20" t="s">
         <v>129</v>
       </c>
       <c r="AZ20" t="str">
         <f t="shared" si="6"/>
-        <v>BA42436CJ</v>
+        <v>BA41818CJ</v>
       </c>
       <c r="BD20" s="33" t="s">
         <v>130</v>
       </c>
       <c r="BE20">
-        <v>355</v>
+        <v>130</v>
       </c>
       <c r="BG20" t="s">
         <v>127</v>
       </c>
       <c r="BH20" t="str">
         <f t="shared" si="7"/>
-        <v>MTKNBN20D20A355A</v>
+        <v>MTKNBN20D20A130A</v>
       </c>
     </row>
     <row r="21" ht="14.5" customHeight="1" spans="49:60" x14ac:dyDescent="0.25">
@@ -2016,27 +2016,27 @@
         <v>124</v>
       </c>
       <c r="AX21">
-        <v>57739</v>
+        <v>30487</v>
       </c>
       <c r="AY21" t="s">
         <v>125</v>
       </c>
       <c r="AZ21" t="str">
         <f t="shared" si="6"/>
-        <v>AB57739JC</v>
+        <v>AB30487JC</v>
       </c>
       <c r="BD21" s="33" t="s">
         <v>126</v>
       </c>
       <c r="BE21">
-        <v>419</v>
+        <v>284</v>
       </c>
       <c r="BG21" t="s">
         <v>127</v>
       </c>
       <c r="BH21" t="str">
         <f t="shared" si="7"/>
-        <v>MTKBNN10D10A419A</v>
+        <v>MTKBNN10D10A284A</v>
       </c>
     </row>
     <row r="22" ht="14.5" customHeight="1" spans="49:60" x14ac:dyDescent="0.25">
@@ -2044,27 +2044,27 @@
         <v>128</v>
       </c>
       <c r="AX22">
-        <v>31447</v>
+        <v>88497</v>
       </c>
       <c r="AY22" t="s">
         <v>129</v>
       </c>
       <c r="AZ22" t="str">
         <f t="shared" si="6"/>
-        <v>BA31447CJ</v>
+        <v>BA88497CJ</v>
       </c>
       <c r="BD22" s="33" t="s">
         <v>130</v>
       </c>
       <c r="BE22">
-        <v>632</v>
+        <v>462</v>
       </c>
       <c r="BG22" t="s">
         <v>127</v>
       </c>
       <c r="BH22" t="str">
         <f t="shared" si="7"/>
-        <v>MTKNBN20D20A632A</v>
+        <v>MTKNBN20D20A462A</v>
       </c>
     </row>
     <row r="23" ht="14.5" customHeight="1" spans="49:60" x14ac:dyDescent="0.25">
@@ -2072,27 +2072,27 @@
         <v>124</v>
       </c>
       <c r="AX23">
-        <v>18459</v>
+        <v>81370</v>
       </c>
       <c r="AY23" t="s">
         <v>125</v>
       </c>
       <c r="AZ23" t="str">
         <f t="shared" si="6"/>
-        <v>AB18459JC</v>
+        <v>AB81370JC</v>
       </c>
       <c r="BD23" s="33" t="s">
         <v>126</v>
       </c>
       <c r="BE23">
-        <v>598</v>
+        <v>135</v>
       </c>
       <c r="BG23" t="s">
         <v>127</v>
       </c>
       <c r="BH23" t="str">
         <f t="shared" si="7"/>
-        <v>MTKBNN10D10A598A</v>
+        <v>MTKBNN10D10A135A</v>
       </c>
     </row>
   </sheetData>
